--- a/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H263"/>
+  <dimension ref="A1:H303"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1696,7 +1696,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ahead.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ。こんな結末は…認められませんの</t>
+          <t xml:space="preserve">下ろしたはずの荷を、また持たされているみたいですわね</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">behind.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1753,14 +1753,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着がつきましたわ。…もう、十分ですの</t>
+          <t xml:space="preserve">終わったことにされた分は、まだお返ししていませんの</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
@@ -1785,14 +1785,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けましたわ。でもこの試合は一生の宝ですわ</t>
+          <t xml:space="preserve">認めませんわ。こんな結末は…認められませんの</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
@@ -1817,14 +1817,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたのおかげで成長できましたわ。これからもよろしくお願いいたしますわ</t>
+          <t xml:space="preserve">決着がつきましたわ。…もう、十分ですの</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">loser.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1849,14 +1849,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日こそ、決着をつけさせていただきますわ</t>
+          <t xml:space="preserve">負けましたわ。でもこの試合は一生の宝ですわ</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.ojousama[1]</t>
+          <t xml:space="preserve">winner.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手させていただきますわ</t>
+          <t xml:space="preserve">あなたのおかげで成長できましたわ。これからもよろしくお願いいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
@@ -1913,14 +1913,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この日を、ずっと待っておりましたわ。全てを賭けますの</t>
+          <t xml:space="preserve">本日こそ、決着をつけさせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="12">
@@ -1945,14 +1945,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ええ、全力でお受けしますわ</t>
+          <t xml:space="preserve">全力でお相手させていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日こそ決着ですわ</t>
+          <t xml:space="preserve">……この日を、ずっと待っておりましたわ。全てを賭けますの</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defender.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。……でも諦めません。……必ず借りを返しますわ</t>
+          <t xml:space="preserve">……ええ、全力でお受けしますわ</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">attacker.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2041,14 +2041,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきましたわ。でもこの因縁はまだ続くのでしょうね</t>
+          <t xml:space="preserve">今日こそ決着ですわ</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">loserLines.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2073,14 +2073,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けましたわ…ですが、この借りは必ずお返ししますわ</t>
+          <t xml:space="preserve">負けました。……でも諦めません。……必ず借りを返しますわ</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">winnerLines.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2105,14 +2105,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつ結果を出しましたわ…でも、まだ終わりではありませんわね</t>
+          <t xml:space="preserve">勝たせていただきましたわ。でもこの因縁はまだ続くのでしょうね</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">loser.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2137,14 +2137,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなはずでは…全力を尽くしましたのに…</t>
+          <t xml:space="preserve">負けましたわ…ですが、この借りは必ずお返ししますわ</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">winner.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ…！ ずっと追いかけてまいりまして…ついに…</t>
+          <t xml:space="preserve">ひとつ結果を出しましたわ…でも、まだ終わりではありませんわね</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2186,29 +2186,29 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.lose[1]</t>
+          <t xml:space="preserve">loserLines.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。……申し訳ありません。</t>
+          <t xml:space="preserve">こんなはずでは…全力を尽くしましたのに…</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.lose[2]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2218,29 +2218,29 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.lose[2]</t>
+          <t xml:space="preserve">winnerLines.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">及びませんでした。悔しくてなりません。</t>
+          <t xml:space="preserve">やりましたわ…！ ずっと追いかけてまいりまして…ついに…</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.lose[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.lose[3]</t>
+          <t xml:space="preserve">ojousama_earnest.lose[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2265,14 +2265,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てませんでした。……この借りは返します。</t>
+          <t xml:space="preserve">負けました。……申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.lose[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.petition[1]</t>
+          <t xml:space="preserve">ojousama_earnest.lose[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2297,14 +2297,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お願いがあります。あの方と戦わせてください。</t>
+          <t xml:space="preserve">及びませんでした。悔しくてなりません。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.lose[3]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.petition[2]</t>
+          <t xml:space="preserve">ojousama_earnest.lose[3]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2329,14 +2329,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくし、あの方と対戦したいのです。どうか。</t>
+          <t xml:space="preserve">勝てませんでした。……この借りは返します。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.petition[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.petition[3]</t>
+          <t xml:space="preserve">ojousama_earnest.petition[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2361,14 +2361,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">願いはひとつです。あの方と、当たらせてください。</t>
+          <t xml:space="preserve">社長、お願いがあります。あの方と戦わせてください。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.petition[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.sendoff[1]</t>
+          <t xml:space="preserve">ojousama_earnest.petition[2]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2393,14 +2393,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。必ず応えます。</t>
+          <t xml:space="preserve">わたくし、あの方と対戦したいのです。どうか。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.petition[3]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.sendoff[2]</t>
+          <t xml:space="preserve">ojousama_earnest.petition[3]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2425,14 +2425,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お許し、無駄にはしません。行ってまいります。</t>
+          <t xml:space="preserve">願いはひとつです。あの方と、当たらせてください。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.sendoff[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.sendoff[3]</t>
+          <t xml:space="preserve">ojousama_earnest.sendoff[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2457,14 +2457,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝します。……全力で戦ってまいります。</t>
+          <t xml:space="preserve">ありがとうございます。必ず応えます。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.sendoff[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.win[1]</t>
+          <t xml:space="preserve">ojousama_earnest.sendoff[2]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2489,14 +2489,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……ありがとうございました。</t>
+          <t xml:space="preserve">お許し、無駄にはしません。行ってまいります。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.sendoff[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.win[2]</t>
+          <t xml:space="preserve">ojousama_earnest.sendoff[3]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2521,14 +2521,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご報告します。勝ってまいりました。</t>
+          <t xml:space="preserve">感謝します。……全力で戦ってまいります。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.win[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.win[3]</t>
+          <t xml:space="preserve">ojousama_earnest.win[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2553,14 +2553,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応えられました。認めてくださったおかげです。</t>
+          <t xml:space="preserve">勝ちました。……ありがとうございました。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.win[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest._accept[1]</t>
+          <t xml:space="preserve">ojousama_earnest.win[2]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2585,14 +2585,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お受けします。全力でお相手します。</t>
+          <t xml:space="preserve">ご報告します。勝ってまいりました。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_earnest.win[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest._accept[2]</t>
+          <t xml:space="preserve">ojousama_earnest.win[3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2617,14 +2617,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名指しの意味、違えずに応えます。</t>
+          <t xml:space="preserve">応えられました。認めてくださったおかげです。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest._accept[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest._accept[3]</t>
+          <t xml:space="preserve">ojousama_earnest._accept[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2649,14 +2649,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたの覚悟に、礼を欠くことはしません。</t>
+          <t xml:space="preserve">お受けします。全力でお相手します。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest._accept[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.draw[1]</t>
+          <t xml:space="preserve">ojousama_earnest._accept[2]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2681,14 +2681,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着をつけられませんでした。心残りです。</t>
+          <t xml:space="preserve">名指しの意味、違えずに応えます。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest._accept[3]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.draw[2]</t>
+          <t xml:space="preserve">ojousama_earnest._accept[3]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2713,14 +2713,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしはまだ納得していません。必ずまた。</t>
+          <t xml:space="preserve">あなたの覚悟に、礼を欠くことはしません。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.draw[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.draw[3]</t>
+          <t xml:space="preserve">ojousama_earnest.draw[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2745,14 +2745,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い出し切りました。それだけは確かです。</t>
+          <t xml:space="preserve">決着をつけられませんでした。心残りです。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.draw[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.lose[1]</t>
+          <t xml:space="preserve">ojousama_earnest.draw[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2777,14 +2777,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの力不足です。言い訳はしません。</t>
+          <t xml:space="preserve">わたくしはまだ納得していません。必ずまた。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.draw[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.lose[2]</t>
+          <t xml:space="preserve">ojousama_earnest.draw[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2809,14 +2809,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗です。悔しさは持ち帰ります。</t>
+          <t xml:space="preserve">お互い出し切りました。それだけは確かです。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.lose[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.lose[3]</t>
+          <t xml:space="preserve">ojousama_earnest.lose[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが上でした。素直に認めます。</t>
+          <t xml:space="preserve">わたくしの力不足です。言い訳はしません。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.lose[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.win[1]</t>
+          <t xml:space="preserve">ojousama_earnest.lose[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2873,14 +2873,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。手は一切抜いていません。</t>
+          <t xml:space="preserve">完敗です。悔しさは持ち帰ります。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.lose[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.win[2]</t>
+          <t xml:space="preserve">ojousama_earnest.lose[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2905,14 +2905,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたは強かった。それは伝えておきます。</t>
+          <t xml:space="preserve">あなたが上でした。素直に認めます。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.win[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_earnest.win[3]</t>
+          <t xml:space="preserve">ojousama_earnest.win[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2937,14 +2937,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちよりも、良い試合だったことが嬉しい。</t>
+          <t xml:space="preserve">勝ちました。手は一切抜いていません。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.win[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2954,29 +2954,29 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama_earnest.win[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しましたわ。やれることがあるなら続けます</t>
+          <t xml:space="preserve">あなたは強かった。それは伝えておきます。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_earnest.win[3]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2986,29 +2986,29 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama_earnest.win[3]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後にもう一度…あのベルトに恥じない闘いをしたいですわ</t>
+          <t xml:space="preserve">勝ちよりも、良い試合だったことが嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accepted.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3033,14 +3033,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しましたわ。お役に立てるなら全力を尽くします</t>
+          <t xml:space="preserve">ここで学んだこと、必ず活かしますわ。本当にお世話になりました</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accepted.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3065,14 +3065,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じてくださって…期待に応えてみせますわ</t>
+          <t xml:space="preserve">感謝しかございません。新しい場所で、必ず結果を出します</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defended.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3097,14 +3097,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後によい試合を。それだけが望みですわ</t>
+          <t xml:space="preserve">…社長のお気持ち、伝わりましたわ。ここで闘い続けます</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defended.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3129,14 +3129,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しましたわ。最後まで演じきれましたもの</t>
+          <t xml:space="preserve">残らせていただきます。必ずご恩をお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defense_failed.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3161,14 +3161,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚悟はできておりましたわ。ありがとうございます</t>
+          <t xml:space="preserve">ご恩をお返しできず、申し訳ございません…新天地で必ず結果を出しますわ</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defense_failed.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3193,14 +3193,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。言ってくださって</t>
+          <t xml:space="preserve">…ごめんなさい。でも、行かなくてはならないんですの</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.earnest.ojousama[1]</t>
+          <t xml:space="preserve">default.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと早く気づくべきでしたわ。…承知しました</t>
+          <t xml:space="preserve">…承知しましたわ。やれることがあるなら続けます</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">former_champ.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3257,14 +3257,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重みをまだ背負えますわ</t>
+          <t xml:space="preserve">最後にもう一度…あのベルトに恥じない闘いをしたいですわ</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">heel.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3289,14 +3289,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体のために尽くしてまいりましたわ</t>
+          <t xml:space="preserve">…承知しましたわ。お役に立てるなら全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">high_trust.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3321,14 +3321,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれることがございます。止まりませんわ</t>
+          <t xml:space="preserve">信じてくださって…期待に応えてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_former_champ.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3353,14 +3353,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の興行で証明いたしますわ</t>
+          <t xml:space="preserve">最後によい試合を。それだけが望みですわ</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_heel.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトに恥じない闘いを…最後まで全うできましたわ</t>
+          <t xml:space="preserve">…承知しましたわ。最後まで演じきれましたもの</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_no_title.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3417,14 +3417,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢には届きませんでしたわ。でもこの道に嘘はございません</t>
+          <t xml:space="preserve">…覚悟はできておりましたわ。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_terminal.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3449,14 +3449,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嫌われ役は…どなたかがやらねばなりませんでしたもの</t>
+          <t xml:space="preserve">ありがとうございますわ。言ってくださって</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_winless.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3481,14 +3481,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で走り抜けましたわ。この時間に嘘はございません</t>
+          <t xml:space="preserve">もっと早く気づくべきでしたわ。…承知しました</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refuse_champ.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3513,14 +3513,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ何もお返しできていませんのに…</t>
+          <t xml:space="preserve">このベルトの重みをまだ背負えますわ</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refuse_distrust.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3545,14 +3545,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りませんでしたわ。もっと…やりたかった</t>
+          <t xml:space="preserve">この団体のために尽くしてまいりましたわ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refuse_fighting.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔いがないとは申しませんわ。でも…やりきりました</t>
+          <t xml:space="preserve">まだやれることがございます。止まりませんわ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refuse_heel.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3609,14 +3609,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の防衛戦…やりたかったですわ</t>
+          <t xml:space="preserve">次の興行で証明いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">A1_champion.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3641,14 +3641,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらに残らせていただきますわ。精進を続けさせてくださいませ</t>
+          <t xml:space="preserve">このベルトに恥じない闘いを…最後まで全うできましたわ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3658,29 +3658,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.earnest.ojousama[1]</t>
+          <t xml:space="preserve">A2_uncrowned.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝いたしますわ。期待に応えてみせますわね。</t>
+          <t xml:space="preserve">夢には届きませんでしたわ。でもこの道に嘘はございません</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3690,29 +3690,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.earnest.ojousama[1]</t>
+          <t xml:space="preserve">A3_heel.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長のご判断を尊重いたしますわ。精一杯やりますわね。</t>
+          <t xml:space="preserve">嫌われ役は…どなたかがやらねばなりませんでしたもの</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3722,29 +3722,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.earnest.ojousama[1]</t>
+          <t xml:space="preserve">A4_veteran.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……残念ですわ。ですが、この判断の結果はお忘れなきよう。</t>
+          <t xml:space="preserve">全力で走り抜けましたわ。この時間に嘘はございません</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3754,29 +3754,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B1_young.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}契約のことで筋を通させていただきたく存じますわ。{record}</t>
+          <t xml:space="preserve">まだ何もお返しできていませんのに…</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3786,29 +3786,29 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B2_prime.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしましたわ。ですが、このまま変わらなければ…。</t>
+          <t xml:space="preserve">まだ足りませんでしたわ。もっと…やりたかった</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3818,29 +3818,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B3_older.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お別れの時が参りました。どうか、お元気で。</t>
+          <t xml:space="preserve">悔いがないとは申しませんわ。でも…やりきりました</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.ojousama[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3850,29 +3850,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.ojousama[2]</t>
+          <t xml:space="preserve">B4_champion_injury.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変お世話になりました。ですが、もう限界でございます。</t>
+          <t xml:space="preserve">最後の防衛戦…やりたかったですわ</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.ojousama[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3882,29 +3882,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。{record}こちらでの経験は一生の宝ですわ。ですが…新天地で挑戦したいのです。</t>
+          <t xml:space="preserve">こちらに残らせていただきますわ。精進を続けさせてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest.ojousama[1]</t>
+          <t xml:space="preserve">raise_accept.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}心苦しいのですが…退団を願い出たく存じますわ。</t>
+          <t xml:space="preserve">感謝いたしますわ。期待に応えてみせますわね。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.earnest.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしましたわ。{tenure_farewell}こちらでの日々、忘れませんわ。{rivalry}</t>
+          <t xml:space="preserve">……社長のご判断を尊重いたしますわ。精一杯やりますわね。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.earnest.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お気持ちは嬉しゅうございますわ。ですが…この決断は揺るぎません。申し訳ございません。</t>
+          <t xml:space="preserve">……残念ですわ。ですが、この判断の結果はお忘れなきよう。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.earnest.ojousama[1]</t>
+          <t xml:space="preserve">raise_open.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4025,401 +4025,401 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……その誠意、しかと受け止めましたわ。もう一度、全力で臨みますわ。</t>
+          <t xml:space="preserve">社長。{tenure}契約のことで筋を通させていただきたく存じますわ。{record}</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知いたしましたわ。ですが、このまま変わらなければ…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お別れの時が参りました。どうか、お元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">大変お世話になりました。ですが、もう限界でございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございますわ。{record}こちらでの経験は一生の宝ですわ。ですが…新天地で挑戦したいのです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}心苦しいのですが…退団を願い出たく存じますわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知いたしましたわ。{tenure_farewell}こちらでの日々、忘れませんわ。{rivalry}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お気持ちは嬉しゅうございますわ。ですが…この決断は揺るぎません。申し訳ございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……その誠意、しかと受け止めましたわ。もう一度、全力で臨みますわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="2">
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr" s="12">
+      <c r="D126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr" s="2">
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今の仲間への責任がありますわ。
 それを果たすまで、他のお話は聞けませんの</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="40" customHeight="1">
-      <c r="A119" t="inlineStr" s="15">
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr" s="12">
+      <c r="D127" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr" s="2">
+      <c r="E127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr" s="3">
+      <c r="F127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">皆さまを置いて行くわけにはまいりませんわ</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr" s="12">
+      <c r="D128" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr" s="2">
+      <c r="E128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr" s="3">
+      <c r="F128" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">この団体を離れるのは容易ではありませんわ。
 …でも、お聞きするだけなら</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="40" customHeight="1">
-      <c r="A121" t="inlineStr" s="15">
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr" s="12">
+      <c r="D129" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr" s="2">
+      <c r="E129" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr" s="3">
+      <c r="F129" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">新しい仲間のために…全力を尽くしますわ。
 よろしくお願いいたします</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、不躾ですが、わたくしどものメンバーをもう少しお気遣いいただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、不躾なお願いですが、次の興行のメインをわたくしたちにお任せいただきたく。</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、お聞き苦しいかもしれませんが、わたくしどもの待遇を見直していただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、不躾なお願いですが、わたくしどもの貢献にひとことお言葉を頂戴したく。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、誠にありがとうございますわ。お言葉、大切にいたします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、誠にありがとうございます。粗相のないよう務めますわ。</t>
-        </is>
-      </c>
-    </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4444,14 +4444,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知いたしましたわ。失礼いたしました。</t>
+          <t xml:space="preserve">社長、不躾ですが、わたくしどものメンバーをもう少しお気遣いいただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">社長、不躾なお願いですが、次の興行のメインをわたくしたちにお任せいただきたく。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4508,14 +4508,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、誠にありがとうございますわ。皆を代表してお礼申し上げますわ。</t>
+          <t xml:space="preserve">社長、お聞き苦しいかもしれませんが、わたくしどもの待遇を見直していただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4540,14 +4540,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
+          <t xml:space="preserve">社長、不躾なお願いですが、わたくしどもの貢献にひとことお言葉を頂戴したく。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4572,14 +4572,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">社長、誠にありがとうございますわ。お言葉、大切にいたします。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、誠にありがとうございますわ。お言葉、大切にいたします。</t>
+          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4636,14 +4636,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4668,14 +4668,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">社長、誠にありがとうございます。粗相のないよう務めますわ。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4700,14 +4700,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。輪の外の子のお気持ち、見えてませんでしたわ。</t>
+          <t xml:space="preserve">…承知いたしましたわ。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4732,14 +4732,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。寛容に甘え過ぎぬよう気をつけますわ。</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ、心がけを改めますわ。</t>
+          <t xml:space="preserve">社長、誠にありがとうございますわ。皆を代表してお礼申し上げますわ。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。</t>
+          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4828,14 +4828,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。リングの外にまで持ち込むのは、行きすぎでしたわ。</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。役柄の責任、まっとういたしますわ。</t>
+          <t xml:space="preserve">社長、誠にありがとうございますわ。お言葉、大切にいたします。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4892,14 +4892,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。お恥ずかしい限りですの。</t>
+          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。お見逃しのぶん、お返しいたしますわ。</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4956,14 +4956,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…申し訳ありませんわ。輪の外の子のお気持ち、見えてませんでしたわ。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4988,14 +4988,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。ご厚意に甘えさせていただきますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。寛容に甘え過ぎぬよう気をつけますわ。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご心配ありがとうございますわ。まだ立てますわ。</t>
+          <t xml:space="preserve">…申し訳ありませんわ、心がけを改めますわ。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5052,14 +5052,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。皆で支えていただけると、立ち直れますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。わたくしの目が届きませんでしたわ。</t>
+          <t xml:space="preserve">…申し訳ありませんわ。リングの外にまで持ち込むのは、行きすぎでしたわ。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。穏便に収まるよう努めますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。役柄の責任、まっとういたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5148,14 +5148,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…申し訳ありませんわ。お恥ずかしい限りですの。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5180,14 +5180,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。心がけを改めます。</t>
+          <t xml:space="preserve">…ありがとうございますわ。お見逃しのぶん、お返しいたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5212,14 +5212,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…静かに会釈なさいましたわ）</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5244,14 +5244,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。ご厚意に甘えさせていただきますわ。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5276,14 +5276,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。わたくしの判断が行きすぎましたわ。</t>
+          <t xml:space="preserve">…ご心配ありがとうございますわ。まだ立てますわ。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。責任はわたくしが持ちますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。皆で支えていただけると、立ち直れますわ。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5340,14 +5340,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…申し訳ありませんわ。わたくしの目が届きませんでしたわ。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.attack.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5372,14 +5372,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">けじめを、つけさせてくださいませ</t>
+          <t xml:space="preserve">…ありがとうございますわ。穏便に収まるよう努めますわ。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.defend.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5404,29 +5404,29 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるつもりはございませんわ</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5436,29 +5436,29 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">心苦しいけれど……わたくし、向こう側で咲きたいのです。</t>
+          <t xml:space="preserve">…申し訳ありませんわ。心がけを改めます。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5468,14 +5468,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来て、退く理由がございませんわ。</t>
+          <t xml:space="preserve">（…静かに会釈なさいましたわ）</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5485,29 +5485,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お稽古の成果ですわ…！ まだまだ上を目指しますわ</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5517,29 +5517,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてまいりましたものが、形になりそうですわ</t>
+          <t xml:space="preserve">…申し訳ありませんわ。わたくしの判断が行きすぎましたわ。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5549,29 +5549,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.earnest.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お稽古の成果が出てきましたわ</t>
+          <t xml:space="preserve">…ありがとうございますわ。責任はわたくしが持ちますわ。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5581,29 +5581,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日お稽古に通うのが…こんなに辛いとは</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.ojousama</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5613,29 +5613,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.attack.ojousama</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘う心を忘れていましたわ…でも、もう迷いませんの</t>
+          <t xml:space="preserve">けじめを、つけさせてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.ojousama</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5645,93 +5645,93 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.defend.ojousama</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしましたわ…必ずお返しいたします</t>
+          <t xml:space="preserve">逃げるつもりはございませんわ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの敗北…わたくしの何がいけませんでしたの</t>
+          <t xml:space="preserve">心苦しいけれど……わたくし、向こう側で咲きたいのです。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できましたのに…まだまだ足りませんわ</t>
+          <t xml:space="preserve">ここまで来て、退く理由がございませんわ。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5756,14 +5756,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できましたわ…でもお体が覚えていますの、あの痛みを</t>
+          <t xml:space="preserve">お稽古の成果ですわ…！ まだまだ上を目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5788,14 +5788,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お怪我は癒えましたわ。でも離れていた時間が…重いですの</t>
+          <t xml:space="preserve">積み重ねてまいりましたものが、形になりそうですわ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5805,29 +5805,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ovr_growth.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合に向けて積み重ねた日々が報われましたわ。最高のお相手に感謝いたします</t>
+          <t xml:space="preserve">お稽古の成果が出てきましたわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5837,29 +5837,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どの試合にも全身全霊を注ぎますわ。それがわたくしの矜持です</t>
+          <t xml:space="preserve">毎日お稽古に通うのが…こんなに辛いとは</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5869,29 +5869,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の皆さまへ。わたくしが歩んだ道を、どうか超えていってくださいまし</t>
+          <t xml:space="preserve">闘う心を忘れていましたわ…でも、もう迷いませんの</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5901,29 +5901,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">弛まぬ努力の賜物ですわ。来年も精進を続けますの</t>
+          <t xml:space="preserve">ご迷惑をおかけしましたわ…必ずお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5933,29 +5933,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defeat.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力を重ねてまいりました。この賞を糧に、さらなる高みを目指しますわ</t>
+          <t xml:space="preserve">あの敗北…わたくしの何がいけませんでしたの</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5965,29 +5965,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングに立つ責任、重々承知しておりますわ</t>
+          <t xml:space="preserve">復帰できましたのに…まだまだ足りませんわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5997,29 +5997,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">injury_severe_recovery.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じぬ試合を、必ずいたしますわ</t>
+          <t xml:space="preserve">復帰できましたわ…でもお体が覚えていますの、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6029,29 +6029,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">penalty_end.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精進の成果、すべてお見せいたしますわ</t>
+          <t xml:space="preserve">お怪我は癒えましたわ。でも離れていた時間が…重いですの</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">bestMatch.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6076,14 +6076,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様、団体として誇らしい限りですわ</t>
+          <t xml:space="preserve">あの試合に向けて積み重ねた日々が報われましたわ。最高のお相手に感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">champion.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6108,14 +6108,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この達成を糧に、さらに精進いたしますわ</t>
+          <t xml:space="preserve">どの試合にも全身全霊を注ぎますわ。それがわたくしの矜持です</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">hallOfFame.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6140,14 +6140,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気を緩めず、次に備えますの</t>
+          <t xml:space="preserve">後輩の皆さまへ。わたくしが歩んだ道を、どうか超えていってくださいまし</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6157,29 +6157,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">mvp.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが大切ですわ。一歩一歩、参りますわね</t>
+          <t xml:space="preserve">弛まぬ努力の賜物ですわ。来年も精進を続けますの</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6189,29 +6189,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rookie.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体でご一緒できる仲間がいて、幸せですわ</t>
+          <t xml:space="preserve">努力を重ねてまいりました。この賞を糧に、さらなる高みを目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6221,29 +6221,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお休みをいただければ、必ず立て直しますわ</t>
+          <t xml:space="preserve">ドームのリングに立つ責任、重々承知しておりますわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6253,29 +6253,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆様のお声が力になりますわ</t>
+          <t xml:space="preserve">団体の名に恥じぬ試合を、必ずいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.ojousama[3]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[3]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切りたいわけではありませんの。ただ……</t>
+          <t xml:space="preserve">精進の成果、すべてお見せいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6317,29 +6317,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を重ねましても、何かが足りない気がしますの…</t>
+          <t xml:space="preserve">満員のお客様、団体として誇らしい限りですわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6349,29 +6349,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…努力が足りないのかしら。でも…</t>
+          <t xml:space="preserve">この達成を糧に、さらに精進いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.ojousama[3]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6381,29 +6381,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[3]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。結果でお応えしますわ</t>
+          <t xml:space="preserve">気を緩めず、次に備えますの</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6413,29 +6413,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みっちり鍛えていただきますわ！絶対に成長してみせますの</t>
+          <t xml:space="preserve">積み重ねが大切ですわ。一歩一歩、参りますわね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6445,29 +6445,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N2.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくださったんですのね…お報いしますわ</t>
+          <t xml:space="preserve">この団体でご一緒できる仲間がいて、幸せですわ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6477,29 +6477,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N3.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみますわ</t>
+          <t xml:space="preserve">少しお休みをいただければ、必ず立て直しますわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6509,29 +6509,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N4.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の看板として恥ずかしくない姿をお見せしますわ</t>
+          <t xml:space="preserve">ファンの皆様のお声が力になりますわ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6541,29 +6541,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N5_low.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、お疲れ様ですわ。明日からまた頑張りましょうね</t>
+          <t xml:space="preserve">裏切りたいわけではありませんの。ただ……</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6573,29 +6573,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N5_warning.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習のことが気になりますけれど…お心遣い、ありがとうございますわ</t>
+          <t xml:space="preserve">練習を重ねましても、何かが足りない気がしますの…</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6605,29 +6605,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.earnest.ojousama[1]</t>
+          <t xml:space="preserve">G1.voice.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そこまでお気遣いを…必ずや復帰してお応えしますわ</t>
+          <t xml:space="preserve">…努力が足りないのかしら。でも…</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bonus.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6652,14 +6652,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をいただけますなんて…全力でお応えしますわ</t>
+          <t xml:space="preserve">ありがとうございます。結果でお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">camp.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6684,14 +6684,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビは緊張いたしますけれど…精一杯やらせていただきますわ</t>
+          <t xml:space="preserve">みっちり鍛えていただきますわ！絶対に成長してみせますの</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest.ojousama[1]</t>
+          <t xml:space="preserve">encourage_high_trust.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6716,14 +6716,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらへの義理がございますから…でも、ご報告だけはと思いまして</t>
+          <t xml:space="preserve">ずっと見てくださったんですのね…お報いしますわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">encourage.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6748,14 +6748,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備してまいりましたの。チャンスをいただけませんこと</t>
+          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみますわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">faction_decree.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6780,14 +6780,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方を越えてこそですわ。組んでいただけませんこと</t>
+          <t xml:space="preserve">わたくしの不徳の致すところ、ということですわね</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest.ojousama[1]</t>
+          <t xml:space="preserve">media.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6812,14 +6812,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チームにご迷惑はかけたくありませんのに…体が限界ですわ…</t>
+          <t xml:space="preserve">団体の看板として恥ずかしくない姿をお見せしますわ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest.ojousama[1]</t>
+          <t xml:space="preserve">party.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6844,14 +6844,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これまで耐えてまいりましたけれど…もう限界ですわ</t>
+          <t xml:space="preserve">皆様、お疲れ様ですわ。明日からまた頑張りましょうね</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refresh_leave.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいですの。特訓のお許しをいただけませんこと</t>
+          <t xml:space="preserve">練習のことが気になりますけれど…お心遣い、ありがとうございますわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest.ojousama[1]</t>
+          <t xml:space="preserve">special_treatment.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6908,14 +6908,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が学んできたことを、後輩にお伝えしたいと思いまして…</t>
+          <t xml:space="preserve">そこまでお気遣いを…必ずや復帰してお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">trainer.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6940,14 +6940,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと気をつけるべきでしたわ…早く復帰して見せますの</t>
+          <t xml:space="preserve">こんな機会をいただけますなんて…全力でお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">E1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…チームのためにもはっきりさせるべきですわ</t>
+          <t xml:space="preserve">テレビは緊張いたしますけれど…精一杯やらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">E6.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7004,14 +7004,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体にご迷惑はかけたくありませんのに…あの方とは…</t>
+          <t xml:space="preserve">こちらへの義理がございますから…でも、ご報告だけはと思いまして</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">品格を忘れず、ブランドのイメージを大切にしますわ</t>
+          <t xml:space="preserve">申し訳ありません…今日はどうしても、体が動かなくて…</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7068,14 +7068,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり準備してお役目を果たしますわ</t>
+          <t xml:space="preserve">稽古に身が入らなくて…申し訳ありません…</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S_grumble.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に誠実に向き合うことが私の務めですわ</t>
+          <t xml:space="preserve">（「わたくし、このままでよろしいのでしょうか」と後輩に弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S_sns.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7132,14 +7132,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイには自信がありますわ。しっかり務めます</t>
+          <t xml:space="preserve">（SNSに「わたくしは本当に必要とされているのでしょうか」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7164,14 +7164,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">プロとして恥ずかしくない撮影ができるよう、準備します</t>
+          <t xml:space="preserve">ずっと準備してまいりましたの。チャンスをいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S2.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7196,14 +7196,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言葉遣いには気をつけて、丁寧に対応しますわ</t>
+          <t xml:space="preserve">あの方を越えてこそですわ。組んでいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S3.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7228,14 +7228,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でよろしいのですか…？ 精一杯頑張りますわ</t>
+          <t xml:space="preserve">チームにご迷惑はかけたくありませんのに…体が限界ですわ…</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7245,29 +7245,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">S4_direct.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
+          <t xml:space="preserve">これまで耐えてまいりましたけれど…もう限界ですわ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7277,29 +7277,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">S4_silent.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
+          <t xml:space="preserve">…………（何か申し上げようと口を開き、そっと閉じた）</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7309,29 +7309,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">S5.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
+          <t xml:space="preserve">もっと強くなりたいですの。特訓のお許しをいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7341,29 +7341,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">S6.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
+          <t xml:space="preserve">私が学んできたことを、後輩にお伝えしたいと思いまして…</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7373,29 +7373,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">B1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
+          <t xml:space="preserve">もっと気をつけるべきでしたわ…早く復帰して見せますの</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">B2_fighter1.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
+          <t xml:space="preserve">あの方とは…チームのためにもはっきりさせるべきですわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7437,29 +7437,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">B2_fighter2.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
+          <t xml:space="preserve">団体にご迷惑はかけたくありませんのに…あの方とは…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7469,29 +7469,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_brand.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
+          <t xml:space="preserve">品格を忘れず、ブランドのイメージを大切にしますわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7501,29 +7501,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_cm.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
+          <t xml:space="preserve">しっかり準備してお役目を果たしますわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.ojousama[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7533,29 +7533,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.ojousama[2]</t>
+          <t xml:space="preserve">B4_fan.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
+          <t xml:space="preserve">ファンの方々に誠実に向き合うことが私の務めですわ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7565,29 +7565,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_fashion.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
+          <t xml:space="preserve">ランウェイには自信がありますわ。しっかり務めます</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7597,29 +7597,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_gravure.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
+          <t xml:space="preserve">プロとして恥ずかしくない撮影ができるよう、準備します</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7629,29 +7629,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_variety.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
+          <t xml:space="preserve">言葉遣いには気をつけて、丁寧に対応しますわ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.ojousama[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7661,29 +7661,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.ojousama[2]</t>
+          <t xml:space="preserve">B4.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
+          <t xml:space="preserve">私でよろしいのですか…？ 精一杯頑張りますわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7708,14 +7708,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
+          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7740,14 +7740,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7772,14 +7772,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
+          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
+          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
+          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7868,14 +7868,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
+          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7900,14 +7900,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
+          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7932,14 +7932,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
+          <t xml:space="preserve">下ろしたはずの荷を、また持たされているみたいですわね</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7964,14 +7964,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
+          <t xml:space="preserve">終わったことにされた分は、まだお返ししていませんの</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">draftInterest.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7996,14 +7996,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
+          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8060,14 +8060,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
+          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8077,29 +8077,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">faGreeting.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切磋琢磨できること、光栄ですわ</t>
+          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8109,29 +8109,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">faSigning.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
+          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8141,29 +8141,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.ojousama[1]</t>
+          <t xml:space="preserve">faWelcome.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
+          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8173,29 +8173,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.ojousama[2]</t>
+          <t xml:space="preserve">injury.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
+          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8205,29 +8205,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.ojousama[1]</t>
+          <t xml:space="preserve">injury.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
+          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8237,29 +8237,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.ojousama[2]</t>
+          <t xml:space="preserve">release.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
+          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8269,29 +8269,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rentalGreeting.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
+          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8301,29 +8301,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.ojousama[2]</t>
+          <t xml:space="preserve">scoutGreeting.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた?</t>
+          <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8333,29 +8333,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
+          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8365,29 +8365,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.ojousama[2]</t>
+          <t xml:space="preserve">titleDefense.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
+          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8397,29 +8397,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.ojousama[1]</t>
+          <t xml:space="preserve">titleLoss.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
+          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8429,29 +8429,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.ojousama[2]</t>
+          <t xml:space="preserve">titleWin.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
+          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8461,29 +8461,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.ojousama[1]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
+          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8493,29 +8493,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.ojousama[2]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
+          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
@@ -8535,19 +8535,19 @@
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
+          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
@@ -8567,19 +8567,19 @@
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
+          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
@@ -8599,19 +8599,19 @@
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てましたわ…！ みなさまのおかげですわ…！</t>
+          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8621,29 +8621,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のために全力を尽くせましたわ…嬉しいですわ</t>
+          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8653,59 +8653,1339 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">bond_39_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
+          <t xml:space="preserve">この関係…繕える自信がありません…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">どこで違えてしまったのでしょう…</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この距離…わたくしの何がいけなかったのでしょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう一度分かり合えるよう、努めなければ</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">切磋琢磨できること、光栄ですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">共に頂を目指したい。二人ならきっと届きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">またとない相方。この巡り合わせに感謝を</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">関わりも変わりました。前へ進みましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの因縁から学んだことは多い。次の目標を探さねば</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">好敵手として意識している自分がおります</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの方を超えることが、今の一番の目標です</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この壁を越えぬ限り、わたくしに先はありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最大の壁。だからこそ、越えねばならないのです</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの存在がわたくしを高めてくれる。これが宿命というものかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">戦えることに感謝を。けれど次は必ず勝ちます</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体に報いられるよう、これからも力を尽くします</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめております</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">信じておりましたのに…もうここでは踏ん張れません</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力を尽くしてきたつもりです。けれど、もう…</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体の方針に…少し不安を覚えます</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしの居場所がここにあるのか…考えてしまいます</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた?</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てましたわ…！ みなさまのおかげですわ…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体のために全力を尽くせましたわ…嬉しいですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr" s="2">
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr" s="12">
+      <c r="D301" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.earnest.ojousama[1]</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr" s="2">
+      <c r="E301" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr" s="3">
+      <c r="F301" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">努力が報われましたわ…感謝しかありませんの</t>
         </is>
       </c>
     </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H263"/>
+  <autoFilter ref="A1:H303"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H303"/>
+  <dimension ref="A1:H302"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -320,7 +320,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.ojousama[1]</t>
+          <t xml:space="preserve">atk.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -352,7 +352,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.ojousama[2]</t>
+          <t xml:space="preserve">atk.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -384,7 +384,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.ojousama[3]</t>
+          <t xml:space="preserve">atk.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -416,7 +416,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.ojousama[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.earnest[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.ojousama[4]</t>
+          <t xml:space="preserve">atk.ojousama.earnest[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -448,7 +448,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bigmove.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -480,7 +480,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.ojousama[2]</t>
+          <t xml:space="preserve">bigmove.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -512,7 +512,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.ojousama[3]</t>
+          <t xml:space="preserve">bigmove.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -544,7 +544,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.ojousama[1]</t>
+          <t xml:space="preserve">climax.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -576,7 +576,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.ojousama[2]</t>
+          <t xml:space="preserve">climax.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -608,7 +608,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -640,7 +640,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -672,7 +672,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -704,7 +704,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">badWinner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -736,7 +736,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">goodWinner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -768,7 +768,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -800,7 +800,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -832,7 +832,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -864,7 +864,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest.ojousama[1]</t>
+          <t xml:space="preserve">competition_won.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -896,7 +896,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest.ojousama[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest.ojousama[2]</t>
+          <t xml:space="preserve">competition_won.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -928,7 +928,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest.ojousama[1]</t>
+          <t xml:space="preserve">direct.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -960,7 +960,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest.ojousama[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest.ojousama[2]</t>
+          <t xml:space="preserve">direct.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -992,7 +992,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest.ojousama[1]</t>
+          <t xml:space="preserve">fa_signing.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1024,7 +1024,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest.ojousama[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest.ojousama[2]</t>
+          <t xml:space="preserve">fa_signing.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1056,7 +1056,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.ojousama.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.earnest.hit[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama.hit[1]</t>
+          <t xml:space="preserve">ojousama.earnest.hit[1]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1088,7 +1088,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.ojousama.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.earnest.hit[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama.hit[2]</t>
+          <t xml:space="preserve">ojousama.earnest.hit[2]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1120,7 +1120,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.ojousama.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.earnest.win[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama.win[1]</t>
+          <t xml:space="preserve">ojousama.earnest.win[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1152,7 +1152,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.ojousama.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.earnest.win[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama.win[2]</t>
+          <t xml:space="preserve">ojousama.earnest.win[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1184,7 +1184,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1216,7 +1216,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1248,7 +1248,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1280,7 +1280,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1312,7 +1312,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1344,7 +1344,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1376,7 +1376,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1408,7 +1408,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1440,7 +1440,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1472,7 +1472,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1504,7 +1504,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1536,7 +1536,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1568,7 +1568,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1600,7 +1600,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1632,7 +1632,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1664,7 +1664,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1696,7 +1696,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ahead.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1728,7 +1728,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.earnest.ojousama[1]</t>
+          <t xml:space="preserve">behind.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1760,7 +1760,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1792,7 +1792,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1824,7 +1824,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1856,7 +1856,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1888,7 +1888,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1920,7 +1920,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1952,7 +1952,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -1984,7 +1984,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2016,7 +2016,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2048,7 +2048,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">loserLines.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2080,7 +2080,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">winnerLines.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2112,7 +2112,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2144,7 +2144,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2176,7 +2176,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">loserLines.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2208,7 +2208,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.ojousama[1]</t>
+          <t xml:space="preserve">winnerLines.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -3008,7 +3008,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accepted.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3040,7 +3040,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.ojousama[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest.ojousama[2]</t>
+          <t xml:space="preserve">accepted.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3072,7 +3072,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defended.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3104,7 +3104,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.ojousama[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest.ojousama[2]</t>
+          <t xml:space="preserve">defended.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3136,7 +3136,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defense_failed.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3168,7 +3168,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.ojousama[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest.ojousama[2]</t>
+          <t xml:space="preserve">defense_failed.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3200,7 +3200,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.earnest.ojousama[1]</t>
+          <t xml:space="preserve">default.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3232,7 +3232,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">former_champ.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3264,7 +3264,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">heel.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3296,7 +3296,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">high_trust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3328,7 +3328,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_former_champ.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3360,7 +3360,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_heel.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3392,7 +3392,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_no_title.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3424,7 +3424,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_terminal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3456,7 +3456,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.earnest.ojousama[1]</t>
+          <t xml:space="preserve">accept_winless.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3488,7 +3488,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refuse_champ.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3520,7 +3520,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refuse_distrust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3552,7 +3552,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refuse_fighting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3584,7 +3584,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refuse_heel.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3616,7 +3616,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">A1_champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3648,7 +3648,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.earnest.ojousama[1]</t>
+          <t xml:space="preserve">A2_uncrowned.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3680,7 +3680,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.earnest.ojousama[1]</t>
+          <t xml:space="preserve">A3_heel.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3712,7 +3712,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.earnest.ojousama[1]</t>
+          <t xml:space="preserve">A4_veteran.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3744,7 +3744,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B1_young.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3776,7 +3776,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B2_prime.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3808,7 +3808,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B3_older.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3840,7 +3840,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_champion_injury.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3872,7 +3872,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3904,7 +3904,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.earnest.ojousama[1]</t>
+          <t xml:space="preserve">raise_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3936,7 +3936,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.earnest.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3968,7 +3968,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.earnest.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4000,7 +4000,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest.ojousama[1]</t>
+          <t xml:space="preserve">raise_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4032,7 +4032,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.earnest.ojousama[1]</t>
+          <t xml:space="preserve">raise_refuse.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4064,7 +4064,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.ojousama[1]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4096,7 +4096,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.ojousama[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.ojousama[2]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4128,7 +4128,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.earnest.ojousama[1]</t>
+          <t xml:space="preserve">transfer_listen.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4160,7 +4160,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest.ojousama[1]</t>
+          <t xml:space="preserve">transfer_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4192,7 +4192,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.earnest.ojousama[1]</t>
+          <t xml:space="preserve">transfer_release.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4224,7 +4224,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.earnest.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4256,7 +4256,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.earnest.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_success.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4288,7 +4288,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.earnest.ojousama[1]</t>
+          <t xml:space="preserve">blocked.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4321,7 +4321,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.earnest.ojousama[1]</t>
+          <t xml:space="preserve">fail.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4353,7 +4353,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.earnest.ojousama[1]</t>
+          <t xml:space="preserve">start.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4386,7 +4386,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.earnest.ojousama[1]</t>
+          <t xml:space="preserve">success.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -5667,7 +5667,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5692,46 +5692,46 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">心苦しいけれど……わたくし、向こう側で咲きたいのです。</t>
+          <t xml:space="preserve">ここまで来て、退く理由がございませんわ。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来て、退く理由がございませんわ。</t>
+          <t xml:space="preserve">お稽古の成果ですわ…！ まだまだ上を目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5756,14 +5756,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お稽古の成果ですわ…！ まだまだ上を目指しますわ</t>
+          <t xml:space="preserve">積み重ねてまいりましたものが、形になりそうですわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ovr_growth.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5788,14 +5788,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてまいりましたものが、形になりそうですわ</t>
+          <t xml:space="preserve">お稽古の成果が出てきましたわ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5820,14 +5820,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お稽古の成果が出てきましたわ</t>
+          <t xml:space="preserve">毎日お稽古に通うのが…こんなに辛いとは</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5852,14 +5852,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日お稽古に通うのが…こんなに辛いとは</t>
+          <t xml:space="preserve">闘う心を忘れていましたわ…でも、もう迷いませんの</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5884,14 +5884,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘う心を忘れていましたわ…でも、もう迷いませんの</t>
+          <t xml:space="preserve">ご迷惑をおかけしましたわ…必ずお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">defeat.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5916,14 +5916,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしましたわ…必ずお返しいたします</t>
+          <t xml:space="preserve">あの敗北…わたくしの何がいけませんでしたの</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest.ojousama[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5948,14 +5948,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの敗北…わたくしの何がいけませんでしたの</t>
+          <t xml:space="preserve">復帰できましたのに…まだまだ足りませんわ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.earnest.ojousama[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5980,14 +5980,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できましたのに…まだまだ足りませんわ</t>
+          <t xml:space="preserve">復帰できましたわ…でもお体が覚えていますの、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.earnest.ojousama[1]</t>
+          <t xml:space="preserve">penalty_end.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6012,14 +6012,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できましたわ…でもお体が覚えていますの、あの痛みを</t>
+          <t xml:space="preserve">お怪我は癒えましたわ。でも離れていた時間が…重いですの</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6029,29 +6029,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bestMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お怪我は癒えましたわ。でも離れていた時間が…重いですの</t>
+          <t xml:space="preserve">あの試合に向けて積み重ねた日々が報われましたわ。最高のお相手に感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest.ojousama[1]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6076,14 +6076,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合に向けて積み重ねた日々が報われましたわ。最高のお相手に感謝いたします</t>
+          <t xml:space="preserve">どの試合にも全身全霊を注ぎますわ。それがわたくしの矜持です</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6108,14 +6108,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どの試合にも全身全霊を注ぎますわ。それがわたくしの矜持です</t>
+          <t xml:space="preserve">後輩の皆さまへ。わたくしが歩んだ道を、どうか超えていってくださいまし</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest.ojousama[1]</t>
+          <t xml:space="preserve">mvp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6140,14 +6140,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の皆さまへ。わたくしが歩んだ道を、どうか超えていってくださいまし</t>
+          <t xml:space="preserve">弛まぬ努力の賜物ですわ。来年も精進を続けますの</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rookie.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6172,14 +6172,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">弛まぬ努力の賜物ですわ。来年も精進を続けますの</t>
+          <t xml:space="preserve">努力を重ねてまいりました。この賞を糧に、さらなる高みを目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6204,14 +6204,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力を重ねてまいりました。この賞を糧に、さらなる高みを目指しますわ</t>
+          <t xml:space="preserve">ドームのリングに立つ責任、重々承知しておりますわ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6236,14 +6236,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングに立つ責任、重々承知しておりますわ</t>
+          <t xml:space="preserve">団体の名に恥じぬ試合を、必ずいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6268,14 +6268,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じぬ試合を、必ずいたしますわ</t>
+          <t xml:space="preserve">精進の成果、すべてお見せいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6300,14 +6300,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精進の成果、すべてお見せいたしますわ</t>
+          <t xml:space="preserve">満員のお客様、団体として誇らしい限りですわ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6332,14 +6332,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様、団体として誇らしい限りですわ</t>
+          <t xml:space="preserve">この達成を糧に、さらに精進いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6364,14 +6364,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この達成を糧に、さらに精進いたしますわ</t>
+          <t xml:space="preserve">気を緩めず、次に備えますの</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6381,29 +6381,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">N1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気を緩めず、次に備えますの</t>
+          <t xml:space="preserve">積み重ねが大切ですわ。一歩一歩、参りますわね</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6428,14 +6428,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが大切ですわ。一歩一歩、参りますわね</t>
+          <t xml:space="preserve">この団体でご一緒できる仲間がいて、幸せですわ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6460,14 +6460,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体でご一緒できる仲間がいて、幸せですわ</t>
+          <t xml:space="preserve">少しお休みをいただければ、必ず立て直しますわ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6492,14 +6492,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお休みをいただければ、必ず立て直しますわ</t>
+          <t xml:space="preserve">ファンの皆様のお声が力になりますわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N5_low.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6524,14 +6524,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆様のお声が力になりますわ</t>
+          <t xml:space="preserve">裏切りたいわけではありませんの。ただ……</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest.ojousama[1]</t>
+          <t xml:space="preserve">N5_warning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切りたいわけではありませんの。ただ……</t>
+          <t xml:space="preserve">練習を重ねましても、何かが足りない気がしますの…</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest.ojousama[1]</t>
+          <t xml:space="preserve">G1.voice.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6588,14 +6588,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を重ねましても、何かが足りない気がしますの…</t>
+          <t xml:space="preserve">…努力が足りないのかしら。でも…</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6605,29 +6605,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bonus.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…努力が足りないのかしら。でも…</t>
+          <t xml:space="preserve">ありがとうございます。結果でお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest.ojousama[1]</t>
+          <t xml:space="preserve">camp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6652,14 +6652,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。結果でお応えしますわ</t>
+          <t xml:space="preserve">みっちり鍛えていただきますわ！絶対に成長してみせますの</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest.ojousama[1]</t>
+          <t xml:space="preserve">encourage_high_trust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6684,14 +6684,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みっちり鍛えていただきますわ！絶対に成長してみせますの</t>
+          <t xml:space="preserve">ずっと見てくださったんですのね…お報いしますわ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest.ojousama[1]</t>
+          <t xml:space="preserve">encourage.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6716,14 +6716,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくださったんですのね…お報いしますわ</t>
+          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみますわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest.ojousama[1]</t>
+          <t xml:space="preserve">faction_decree.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6748,14 +6748,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみますわ</t>
+          <t xml:space="preserve">わたくしの不徳の致すところ、ということですわね</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.earnest.ojousama[1]</t>
+          <t xml:space="preserve">media.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6780,14 +6780,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの不徳の致すところ、ということですわね</t>
+          <t xml:space="preserve">団体の看板として恥ずかしくない姿をお見せしますわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest.ojousama[1]</t>
+          <t xml:space="preserve">party.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6812,14 +6812,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の看板として恥ずかしくない姿をお見せしますわ</t>
+          <t xml:space="preserve">皆様、お疲れ様ですわ。明日からまた頑張りましょうね</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest.ojousama[1]</t>
+          <t xml:space="preserve">refresh_leave.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6844,14 +6844,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、お疲れ様ですわ。明日からまた頑張りましょうね</t>
+          <t xml:space="preserve">練習のことが気になりますけれど…お心遣い、ありがとうございますわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest.ojousama[1]</t>
+          <t xml:space="preserve">special_treatment.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習のことが気になりますけれど…お心遣い、ありがとうございますわ</t>
+          <t xml:space="preserve">そこまでお気遣いを…必ずや復帰してお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.earnest.ojousama[1]</t>
+          <t xml:space="preserve">trainer.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6908,14 +6908,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そこまでお気遣いを…必ずや復帰してお応えしますわ</t>
+          <t xml:space="preserve">こんな機会をいただけますなんて…全力でお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest.ojousama[1]</t>
+          <t xml:space="preserve">E1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6940,14 +6940,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をいただけますなんて…全力でお応えしますわ</t>
+          <t xml:space="preserve">テレビは緊張いたしますけれど…精一杯やらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">E6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビは緊張いたしますけれど…精一杯やらせていただきますわ</t>
+          <t xml:space="preserve">こちらへの義理がございますから…でも、ご報告だけはと思いまして</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7004,14 +7004,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらへの義理がございますから…でも、ご報告だけはと思いまして</t>
+          <t xml:space="preserve">申し訳ありません…今日はどうしても、体が動かなくて…</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…今日はどうしても、体が動かなくて…</t>
+          <t xml:space="preserve">稽古に身が入らなくて…申し訳ありません…</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.ojousama[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest.ojousama[2]</t>
+          <t xml:space="preserve">S_grumble.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7068,14 +7068,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">稽古に身が入らなくて…申し訳ありません…</t>
+          <t xml:space="preserve">（「わたくし、このままでよろしいのでしょうか」と後輩に弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S_sns.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「わたくし、このままでよろしいのでしょうか」と後輩に弱音を漏らしている）</t>
+          <t xml:space="preserve">（SNSに「わたくしは本当に必要とされているのでしょうか」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7132,14 +7132,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「わたくしは本当に必要とされているのでしょうか」と率直な投稿）</t>
+          <t xml:space="preserve">ずっと準備してまいりましたの。チャンスをいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7164,14 +7164,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備してまいりましたの。チャンスをいただけませんこと</t>
+          <t xml:space="preserve">あの方を越えてこそですわ。組んでいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7196,14 +7196,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方を越えてこそですわ。組んでいただけませんこと</t>
+          <t xml:space="preserve">チームにご迷惑はかけたくありませんのに…体が限界ですわ…</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S4_direct.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7228,14 +7228,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チームにご迷惑はかけたくありませんのに…体が限界ですわ…</t>
+          <t xml:space="preserve">これまで耐えてまいりましたけれど…もう限界ですわ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S4_silent.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7260,14 +7260,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これまで耐えてまいりましたけれど…もう限界ですわ</t>
+          <t xml:space="preserve">…………（何か申し上げようと口を開き、そっと閉じた）</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S5.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7292,14 +7292,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何か申し上げようと口を開き、そっと閉じた）</t>
+          <t xml:space="preserve">もっと強くなりたいですの。特訓のお許しをいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.earnest.ojousama[1]</t>
+          <t xml:space="preserve">S6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7324,14 +7324,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいですの。特訓のお許しをいただけませんこと</t>
+          <t xml:space="preserve">私が学んできたことを、後輩にお伝えしたいと思いまして…</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7356,14 +7356,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が学んできたことを、後輩にお伝えしたいと思いまして…</t>
+          <t xml:space="preserve">もっと気をつけるべきでしたわ…早く復帰して見せますの</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B2_fighter1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7388,14 +7388,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと気をつけるべきでしたわ…早く復帰して見せますの</t>
+          <t xml:space="preserve">あの方とは…チームのためにもはっきりさせるべきですわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B2_fighter2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7420,14 +7420,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…チームのためにもはっきりさせるべきですわ</t>
+          <t xml:space="preserve">団体にご迷惑はかけたくありませんのに…あの方とは…</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_brand.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7452,14 +7452,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体にご迷惑はかけたくありませんのに…あの方とは…</t>
+          <t xml:space="preserve">品格を忘れず、ブランドのイメージを大切にしますわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_cm.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7484,14 +7484,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">品格を忘れず、ブランドのイメージを大切にしますわ</t>
+          <t xml:space="preserve">しっかり準備してお役目を果たしますわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_fan.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7516,14 +7516,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり準備してお役目を果たしますわ</t>
+          <t xml:space="preserve">ファンの方々に誠実に向き合うことが私の務めですわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_fashion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7548,14 +7548,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に誠実に向き合うことが私の務めですわ</t>
+          <t xml:space="preserve">ランウェイには自信がありますわ。しっかり務めます</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_gravure.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7580,14 +7580,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイには自信がありますわ。しっかり務めます</t>
+          <t xml:space="preserve">プロとして恥ずかしくない撮影ができるよう、準備します</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4_variety.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">プロとして恥ずかしくない撮影ができるよう、準備します</t>
+          <t xml:space="preserve">言葉遣いには気をつけて、丁寧に対応しますわ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.earnest.ojousama[1]</t>
+          <t xml:space="preserve">B4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7644,14 +7644,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言葉遣いには気をつけて、丁寧に対応しますわ</t>
+          <t xml:space="preserve">私でよろしいのですか…？ 精一杯頑張りますわ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7661,29 +7661,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でよろしいのですか…？ 精一杯頑張りますわ</t>
+          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7708,14 +7708,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7740,14 +7740,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
+          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7772,14 +7772,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
+          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
+          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
+          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7868,14 +7868,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
+          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7900,14 +7900,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
+          <t xml:space="preserve">下ろしたはずの荷を、また持たされているみたいですわね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7932,14 +7932,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">下ろしたはずの荷を、また持たされているみたいですわね</t>
+          <t xml:space="preserve">終わったことにされた分は、まだお返ししていませんの</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.earnest.ojousama[1]</t>
+          <t xml:space="preserve">draftInterest.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7964,14 +7964,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったことにされた分は、まだお返ししていませんの</t>
+          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7996,14 +7996,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
+          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.ojousama[2]</t>
+          <t xml:space="preserve">faGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8060,14 +8060,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
+          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8092,14 +8092,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest.ojousama[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8124,14 +8124,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
+          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest.ojousama[1]</t>
+          <t xml:space="preserve">injury.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8156,14 +8156,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
+          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.ojousama[1]</t>
+          <t xml:space="preserve">injury.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8188,14 +8188,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
+          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.ojousama[2]</t>
+          <t xml:space="preserve">release.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8220,14 +8220,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
+          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8252,14 +8252,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
+          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8284,14 +8284,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
+          <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.earnest.ojousama[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
+          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest.ojousama[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8348,14 +8348,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
+          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest.ojousama[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
+          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest.ojousama[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8412,14 +8412,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
+          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
+          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8476,14 +8476,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
+          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8508,14 +8508,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
+          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8540,14 +8540,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
+          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8572,14 +8572,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
+          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8604,14 +8604,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
+          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8621,29 +8621,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
+          <t xml:space="preserve">この関係…繕える自信がありません…</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8668,14 +8668,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この関係…繕える自信がありません…</t>
+          <t xml:space="preserve">どこで違えてしまったのでしょう…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">bond_59_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8700,14 +8700,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこで違えてしまったのでしょう…</t>
+          <t xml:space="preserve">この距離…わたくしの何がいけなかったのでしょう</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8732,14 +8732,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この距離…わたくしの何がいけなかったのでしょう</t>
+          <t xml:space="preserve">もう一度分かり合えるよう、努めなければ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">bond_60_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8764,14 +8764,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度分かり合えるよう、努めなければ</t>
+          <t xml:space="preserve">切磋琢磨できること、光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8796,14 +8796,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切磋琢磨できること、光栄ですわ</t>
+          <t xml:space="preserve">共に頂を目指したい。二人ならきっと届きます</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8828,14 +8828,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">共に頂を目指したい。二人ならきっと届きます</t>
+          <t xml:space="preserve">またとない相方。この巡り合わせに感謝を</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8860,14 +8860,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またとない相方。この巡り合わせに感謝を</t>
+          <t xml:space="preserve">関わりも変わりました。前へ進みましょう</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8892,14 +8892,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関わりも変わりました。前へ進みましょう</t>
+          <t xml:space="preserve">あの因縁から学んだことは多い。次の目標を探さねば</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8924,14 +8924,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁から学んだことは多い。次の目標を探さねば</t>
+          <t xml:space="preserve">好敵手として意識している自分がおります</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8956,14 +8956,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好敵手として意識している自分がおります</t>
+          <t xml:space="preserve">あの方を超えることが、今の一番の目標です</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8988,14 +8988,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方を超えることが、今の一番の目標です</t>
+          <t xml:space="preserve">この壁を越えぬ限り、わたくしに先はありません</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9020,14 +9020,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この壁を越えぬ限り、わたくしに先はありません</t>
+          <t xml:space="preserve">最大の壁。だからこそ、越えねばならないのです</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最大の壁。だからこそ、越えねばならないのです</t>
+          <t xml:space="preserve">あの存在がわたくしを高めてくれる。これが宿命というものかしら</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9084,14 +9084,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの存在がわたくしを高めてくれる。これが宿命というものかしら</t>
+          <t xml:space="preserve">戦えることに感謝を。けれど次は必ず勝ちます</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">trust_above_75.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9116,14 +9116,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戦えることに感謝を。けれど次は必ず勝ちます</t>
+          <t xml:space="preserve">この団体に報いられるよう、これからも力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.ojousama[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9148,14 +9148,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に報いられるよう、これからも力を尽くします</t>
+          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめております</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.ojousama[2]</t>
+          <t xml:space="preserve">trust_below_20.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9180,14 +9180,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめております</t>
+          <t xml:space="preserve">信じておりましたのに…もうここでは踏ん張れません</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じておりましたのに…もうここでは踏ん張れません</t>
+          <t xml:space="preserve">全力を尽くしてきたつもりです。けれど、もう…</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.ojousama[2]</t>
+          <t xml:space="preserve">trust_below_35.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9244,14 +9244,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くしてきたつもりです。けれど、もう…</t>
+          <t xml:space="preserve">この団体の方針に…少し不安を覚えます</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の方針に…少し不安を覚えます</t>
+          <t xml:space="preserve">わたくしの居場所がここにあるのか…考えてしまいます</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9308,14 +9308,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの居場所がここにあるのか…考えてしまいます</t>
+          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9325,29 +9325,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
+          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9372,14 +9372,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
+          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.ojousama[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9404,14 +9404,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
+          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.ojousama[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9436,14 +9436,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
+          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.ojousama[2]</t>
+          <t xml:space="preserve">survivor.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9468,14 +9468,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
+          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.ojousama[1]</t>
+          <t xml:space="preserve">survivor.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9500,14 +9500,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
+          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた?</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.ojousama[2]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9532,14 +9532,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた?</t>
+          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.ojousama[1]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9564,14 +9564,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
+          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.ojousama[2]</t>
+          <t xml:space="preserve">defiant.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9596,14 +9596,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
+          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.ojousama[1]</t>
+          <t xml:space="preserve">defiant.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9628,14 +9628,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
+          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.ojousama[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
+          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.ojousama[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
+          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.ojousama[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9724,14 +9724,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
+          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9756,14 +9756,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
+          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9788,14 +9788,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
+          <t xml:space="preserve">勝てましたわ…！ みなさまのおかげですわ…！</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てましたわ…！ みなさまのおかげですわ…！</t>
+          <t xml:space="preserve">団体のために全力を尽くせましたわ…嬉しいですわ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.ojousama[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のために全力を尽くせましたわ…嬉しいですわ</t>
+          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.ojousama[3]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9869,29 +9869,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[3]</t>
+          <t xml:space="preserve">fighter.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
+          <t xml:space="preserve">努力が報われましたわ…感謝しかありませんの</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.earnest.ojousama[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9901,29 +9901,29 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…感謝しかありませんの</t>
+          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.earnest.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9948,44 +9948,12 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="40" customHeight="1">
-      <c r="A303" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">earnest.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H303"/>
+  <autoFilter ref="A1:H302"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">真剣勝負ですわ…参りますわよ！</t>
+          <t xml:space="preserve">真剣勝負です…参りますわよ！</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイミングを合わせて！</t>
+          <t xml:space="preserve">タイミングを合わせますわ！</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よく耐えましたわ、交代ですわ！</t>
+          <t xml:space="preserve">よく耐えました、交代ですわ！</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けましたわ。でもこの試合は一生の宝ですわ</t>
+          <t xml:space="preserve">負けました。でもこの試合は一生の宝ですわ</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたのおかげで成長できましたわ。これからもよろしくお願いいたしますわ</t>
+          <t xml:space="preserve">あなたのおかげで成長できました。これからもよろしくお願いいたしますわ</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けましたわ…ですが、この借りは必ずお返ししますわ</t>
+          <t xml:space="preserve">負けました…ですが、この借りは必ずお返ししますわ</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつ結果を出しましたわ…でも、まだ終わりではありませんわね</t>
+          <t xml:space="preserve">ひとつ結果を出しました…でも、まだ終わりではありませんわね</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちよりも、良い試合だったことが嬉しい。</t>
+          <t xml:space="preserve">勝ちよりも、良い試合だったことが嬉しいですの。</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝いたしますわ。期待に応えてみせますわね。</t>
+          <t xml:space="preserve">感謝いたします。期待に応えてみせますわね。</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長のご判断を尊重いたしますわ。精一杯やりますわね。</t>
+          <t xml:space="preserve">……社長のご判断を尊重いたします。精一杯やりますわね。</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。{record}こちらでの経験は一生の宝ですわ。ですが…新天地で挑戦したいのです。</t>
+          <t xml:space="preserve">ありがとうございます。{record}こちらでの経験は一生の宝ですわ。ですが…新天地で挑戦したいのです。</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしましたわ。{tenure_farewell}こちらでの日々、忘れませんわ。{rivalry}</t>
+          <t xml:space="preserve">……承知いたしました。{tenure_farewell}こちらでの日々、忘れませんわ。{rivalry}</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……その誠意、しかと受け止めましたわ。もう一度、全力で臨みますわ。</t>
+          <t xml:space="preserve">……その誠意、しかと受け止めました。もう一度、全力で臨みますわ。</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、誠にありがとうございますわ。皆を代表してお礼申し上げますわ。</t>
+          <t xml:space="preserve">社長、誠にありがとうございます。皆を代表してお礼申し上げますわ。</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。輪の外の子のお気持ち、見えてませんでしたわ。</t>
+          <t xml:space="preserve">…申し訳ありません。輪の外の子のお気持ち、見えてませんでしたわ。</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。寛容に甘え過ぎぬよう気をつけますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎぬよう気をつけますわ。</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ、心がけを改めますわ。</t>
+          <t xml:space="preserve">…申し訳ありません、心がけを改めますわ。</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。リングの外にまで持ち込むのは、行きすぎでしたわ。</t>
+          <t xml:space="preserve">…申し訳ありません。リングの外にまで持ち込むのは、行きすぎでしたわ。</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。役柄の責任、まっとういたしますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとういたしますわ。</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。お見逃しのぶん、お返しいたしますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。お見逃しのぶん、お返しいたしますわ。</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。ご厚意に甘えさせていただきますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。ご厚意に甘えさせていただきますわ。</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご心配ありがとうございますわ。まだ立てますわ。</t>
+          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てますわ。</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。皆で支えていただけると、立ち直れますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。皆で支えていただけると、立ち直れますわ。</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。わたくしの目が届きませんでしたわ。</t>
+          <t xml:space="preserve">…申し訳ありません。わたくしの目が届きませんでしたわ。</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。穏便に収まるよう努めますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。穏便に収まるよう努めますわ。</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。わたくしの判断が行きすぎましたわ。</t>
+          <t xml:space="preserve">…申し訳ありません。わたくしの判断が行きすぎましたわ。</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。責任はわたくしが持ちますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。責任はわたくしが持ちますわ。</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お稽古の成果ですわ…！ まだまだ上を目指しますわ</t>
+          <t xml:space="preserve">お稽古の成果です…！ まだまだ上を目指しますわ</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6019,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">autumnWarChampion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6044,14 +6044,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合に向けて積み重ねた日々が報われましたわ。最高のお相手に感謝いたします</t>
+          <t xml:space="preserve">団体を代表する責任を果たせたことを、誇りに思いますわ。</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">bestMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6076,14 +6076,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どの試合にも全身全霊を注ぎますわ。それがわたくしの矜持です</t>
+          <t xml:space="preserve">あの試合に向けて積み重ねた日々が報われましたわ。最高のお相手に感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.ojousama.earnest[1]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6108,14 +6108,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の皆さまへ。わたくしが歩んだ道を、どうか超えていってくださいまし</t>
+          <t xml:space="preserve">どの試合にも全身全霊を注ぎますわ。それがわたくしの矜持です</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.ojousama.earnest[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6140,14 +6140,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">弛まぬ努力の賜物ですわ。来年も精進を続けますの</t>
+          <t xml:space="preserve">後輩の皆さまへ。わたくしが歩んだ道を、どうか超えていってくださいまし</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.ojousama.earnest[1]</t>
+          <t xml:space="preserve">mvp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6172,14 +6172,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力を重ねてまいりました。この賞を糧に、さらなる高みを目指しますわ</t>
+          <t xml:space="preserve">弛まぬ努力の賜物ですわ。来年も精進を続けますの</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">rookie.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6204,14 +6204,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングに立つ責任、重々承知しておりますわ</t>
+          <t xml:space="preserve">努力を重ねてまいりました。この賞を糧に、さらなる高みを目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">springTagChampion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6236,14 +6236,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じぬ試合を、必ずいたしますわ</t>
+          <t xml:space="preserve">相棒の献身に報いるためにも、この優勝を誇り高く受け取りますわ。</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[3]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6268,14 +6268,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精進の成果、すべてお見せいたしますわ</t>
+          <t xml:space="preserve">ドームのリングに立つ責任、重々承知しておりますわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6300,14 +6300,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様、団体として誇らしい限りですわ</t>
+          <t xml:space="preserve">団体の名に恥じぬ試合を、必ずいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6332,14 +6332,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この達成を糧に、さらに精進いたしますわ</t>
+          <t xml:space="preserve">精進の成果、すべてお見せいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[3]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6364,14 +6364,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気を緩めず、次に備えますの</t>
+          <t xml:space="preserve">満員のお客様、団体として誇らしい限りですわ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6381,29 +6381,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが大切ですわ。一歩一歩、参りますわね</t>
+          <t xml:space="preserve">この達成を糧に、さらに精進いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6413,29 +6413,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体でご一緒できる仲間がいて、幸せですわ</t>
+          <t xml:space="preserve">気を緩めず、次に備えますの</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6460,14 +6460,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお休みをいただければ、必ず立て直しますわ</t>
+          <t xml:space="preserve">積み重ねが大切です。一歩一歩、参りますわね</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6492,14 +6492,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆様のお声が力になりますわ</t>
+          <t xml:space="preserve">この団体でご一緒できる仲間がいて、幸せですわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6524,14 +6524,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切りたいわけではありませんの。ただ……</t>
+          <t xml:space="preserve">少しお休みをいただければ、必ず立て直しますわ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を重ねましても、何かが足りない気がしますの…</t>
+          <t xml:space="preserve">ファンの皆様のお声が力になりますわ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N5_low.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6588,14 +6588,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…努力が足りないのかしら。でも…</t>
+          <t xml:space="preserve">裏切りたいわけではありませんの。ただ……</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6605,29 +6605,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。結果でお応えしますわ</t>
+          <t xml:space="preserve">練習を重ねましても、何かが足りない気がしますの…</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6637,29 +6637,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.ojousama.earnest[1]</t>
+          <t xml:space="preserve">G1.voice.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みっちり鍛えていただきますわ！絶対に成長してみせますの</t>
+          <t xml:space="preserve">…努力が足りないのかしら。でも…</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.ojousama.earnest[1]</t>
+          <t xml:space="preserve">bonus.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6684,14 +6684,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくださったんですのね…お報いしますわ</t>
+          <t xml:space="preserve">ありがとうございます。結果でお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.ojousama.earnest[1]</t>
+          <t xml:space="preserve">camp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6716,14 +6716,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみますわ</t>
+          <t xml:space="preserve">みっちり鍛えていただきますわ！絶対に成長してみせますの</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.ojousama.earnest[1]</t>
+          <t xml:space="preserve">encourage_high_trust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6748,14 +6748,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの不徳の致すところ、ということですわね</t>
+          <t xml:space="preserve">ずっと見てくださったんですのね…お報いしますわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.ojousama.earnest[1]</t>
+          <t xml:space="preserve">encourage.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6780,14 +6780,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の看板として恥ずかしくない姿をお見せしますわ</t>
+          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみますわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.ojousama.earnest[1]</t>
+          <t xml:space="preserve">faction_decree.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6812,14 +6812,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、お疲れ様ですわ。明日からまた頑張りましょうね</t>
+          <t xml:space="preserve">わたくしの不徳の致すところ、ということですわね</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.ojousama.earnest[1]</t>
+          <t xml:space="preserve">media.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6844,14 +6844,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習のことが気になりますけれど…お心遣い、ありがとうございますわ</t>
+          <t xml:space="preserve">団体の看板として恥ずかしくない姿をお見せしますわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.ojousama.earnest[1]</t>
+          <t xml:space="preserve">party.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そこまでお気遣いを…必ずや復帰してお応えしますわ</t>
+          <t xml:space="preserve">皆様、お疲れ様ですわ。明日からまた頑張りましょうね</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.ojousama.earnest[1]</t>
+          <t xml:space="preserve">refresh_leave.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6908,14 +6908,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をいただけますなんて…全力でお応えしますわ</t>
+          <t xml:space="preserve">練習のことが気になりますけれど…お心遣い、ありがとうございますわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">special_treatment.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6940,14 +6940,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビは緊張いたしますけれど…精一杯やらせていただきますわ</t>
+          <t xml:space="preserve">そこまでお気遣いを…必ずや復帰してお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.ojousama.earnest[1]</t>
+          <t xml:space="preserve">trainer.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらへの義理がございますから…でも、ご報告だけはと思いまして</t>
+          <t xml:space="preserve">こんな機会をいただけますなんて…全力でお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.earnest[1]</t>
+          <t xml:space="preserve">E1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7004,14 +7004,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…今日はどうしても、体が動かなくて…</t>
+          <t xml:space="preserve">テレビは緊張いたしますけれど…精一杯やらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.earnest[2]</t>
+          <t xml:space="preserve">E6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">稽古に身が入らなくて…申し訳ありません…</t>
+          <t xml:space="preserve">こちらへの義理がございますから…でも、ご報告だけはと思いまして</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7068,14 +7068,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「わたくし、このままでよろしいのでしょうか」と後輩に弱音を漏らしている）</t>
+          <t xml:space="preserve">申し訳ありません…今日はどうしても、体が動かなくて…</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「わたくしは本当に必要とされているのでしょうか」と率直な投稿）</t>
+          <t xml:space="preserve">稽古に身が入らなくて…申し訳ありません…</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S_grumble.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7132,14 +7132,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備してまいりましたの。チャンスをいただけませんこと</t>
+          <t xml:space="preserve">（「わたくし、このままでよろしいのでしょうか」と後輩に弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S_sns.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7164,14 +7164,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方を越えてこそですわ。組んでいただけませんこと</t>
+          <t xml:space="preserve">（SNSに「わたくしは本当に必要とされているのでしょうか」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7196,14 +7196,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チームにご迷惑はかけたくありませんのに…体が限界ですわ…</t>
+          <t xml:space="preserve">ずっと準備してまいりましたの。チャンスをいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7228,14 +7228,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これまで耐えてまいりましたけれど…もう限界ですわ</t>
+          <t xml:space="preserve">あの方を越えてこそですわ。組んでいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7260,14 +7260,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何か申し上げようと口を開き、そっと閉じた）</t>
+          <t xml:space="preserve">チームにご迷惑はかけたくありませんのに…体が限界ですわ…</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7292,14 +7292,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいですの。特訓のお許しをいただけませんこと</t>
+          <t xml:space="preserve">これまで耐えてまいりましたけれど…もう限界ですわ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S4_silent.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7324,14 +7324,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が学んできたことを、後輩にお伝えしたいと思いまして…</t>
+          <t xml:space="preserve">…………（何か申し上げようと口を開き、そっと閉じた）</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S5.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7356,14 +7356,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと気をつけるべきでしたわ…早く復帰して見せますの</t>
+          <t xml:space="preserve">もっと強くなりたいですの。特訓のお許しをいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7388,14 +7388,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…チームのためにもはっきりさせるべきですわ</t>
+          <t xml:space="preserve">私が学んできたことを、後輩にお伝えしたいと思いまして…</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7420,14 +7420,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体にご迷惑はかけたくありませんのに…あの方とは…</t>
+          <t xml:space="preserve">もっと気をつけるべきでしたわ…早く復帰して見せますの</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7452,14 +7452,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">品格を忘れず、ブランドのイメージを大切にしますわ</t>
+          <t xml:space="preserve">あの方とは…チームのためにもはっきりさせるべきですわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7484,14 +7484,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり準備してお役目を果たしますわ</t>
+          <t xml:space="preserve">団体にご迷惑はかけたくありませんのに…あの方とは…</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_brand.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7516,14 +7516,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に誠実に向き合うことが私の務めですわ</t>
+          <t xml:space="preserve">品格を忘れず、ブランドのイメージを大切にしますわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_cm.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7548,14 +7548,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイには自信がありますわ。しっかり務めます</t>
+          <t xml:space="preserve">しっかり準備してお役目を果たしますわ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_fan.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7580,14 +7580,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">プロとして恥ずかしくない撮影ができるよう、準備します</t>
+          <t xml:space="preserve">ファンの方々に誠実に向き合うことが私の務めですわ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_fashion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言葉遣いには気をつけて、丁寧に対応しますわ</t>
+          <t xml:space="preserve">ランウェイには自信がありますわ。しっかり務めます</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_gravure.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7644,14 +7644,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でよろしいのですか…？ 精一杯頑張りますわ</t>
+          <t xml:space="preserve">プロとして恥ずかしくない撮影ができるよう、準備します</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7661,29 +7661,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_variety.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
+          <t xml:space="preserve">言葉遣いには気をつけて、丁寧に対応しますわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7693,29 +7693,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
+          <t xml:space="preserve">私でよろしいのですか…？ 精一杯頑張りますわ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7740,14 +7740,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
+          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
@@ -7772,14 +7772,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
+          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
+          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7868,14 +7868,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
+          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7900,14 +7900,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">下ろしたはずの荷を、また持たされているみたいですわね</t>
+          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7932,14 +7932,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったことにされた分は、まだお返ししていませんの</t>
+          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7964,14 +7964,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
+          <t xml:space="preserve">下ろしたはずの荷を、また持たされているみたいですわね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7996,14 +7996,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
+          <t xml:space="preserve">終わったことにされた分は、まだお返ししていませんの</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.earnest[2]</t>
+          <t xml:space="preserve">draftInterest.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
+          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8060,14 +8060,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8092,14 +8092,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
+          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.earnest[1]</t>
+          <t xml:space="preserve">faGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8124,14 +8124,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
+          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.earnest[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8156,14 +8156,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
+          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.earnest[2]</t>
+          <t xml:space="preserve">faWelcome.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8188,14 +8188,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
+          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.earnest[1]</t>
+          <t xml:space="preserve">injury.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8220,14 +8220,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
+          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">injury.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8252,14 +8252,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
+          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">release.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8284,14 +8284,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
+          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.earnest[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
+          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.earnest[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8348,14 +8348,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
+          <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.earnest[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
+          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.earnest[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8412,14 +8412,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
+          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
+          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8476,14 +8476,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
+          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
@@ -8508,14 +8508,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
+          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
@@ -8540,14 +8540,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
+          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
@@ -8572,14 +8572,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
+          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
@@ -8604,14 +8604,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
+          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8621,29 +8621,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この関係…繕える自信がありません…</t>
+          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8653,29 +8653,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこで違えてしまったのでしょう…</t>
+          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8700,14 +8700,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この距離…わたくしの何がいけなかったのでしょう</t>
+          <t xml:space="preserve">この関係…繕える自信がありません…</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">bond_39_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8732,14 +8732,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度分かり合えるよう、努めなければ</t>
+          <t xml:space="preserve">どこで違えてしまったのでしょう…</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8764,14 +8764,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切磋琢磨できること、光栄ですわ</t>
+          <t xml:space="preserve">この距離…わたくしの何がいけなかったのでしょう</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8796,14 +8796,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">共に頂を目指したい。二人ならきっと届きます</t>
+          <t xml:space="preserve">もう一度分かり合えるよう、努めなければ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">bond_60_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8828,14 +8828,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またとない相方。この巡り合わせに感謝を</t>
+          <t xml:space="preserve">切磋琢磨できること、光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8860,14 +8860,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関わりも変わりました。前へ進みましょう</t>
+          <t xml:space="preserve">共に頂を目指したい。二人ならきっと届きます</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">bond_80_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8892,14 +8892,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁から学んだことは多い。次の目標を探さねば</t>
+          <t xml:space="preserve">またとない相方。この巡り合わせに感謝を</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8924,14 +8924,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好敵手として意識している自分がおります</t>
+          <t xml:space="preserve">関わりも変わりました。前へ進みましょう</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8956,14 +8956,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方を超えることが、今の一番の目標です</t>
+          <t xml:space="preserve">あの因縁から学んだことは多い。次の目標を探さねば</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8988,14 +8988,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この壁を越えぬ限り、わたくしに先はありません</t>
+          <t xml:space="preserve">好敵手として意識している自分がおります</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9020,14 +9020,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最大の壁。だからこそ、越えねばならないのです</t>
+          <t xml:space="preserve">あの方を超えることが、今の一番の目標です</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの存在がわたくしを高めてくれる。これが宿命というものかしら</t>
+          <t xml:space="preserve">この壁を越えぬ限り、わたくしに先はありません</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9084,14 +9084,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戦えることに感謝を。けれど次は必ず勝ちます</t>
+          <t xml:space="preserve">最大の壁。だからこそ、越えねばならないのです</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9116,14 +9116,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に報いられるよう、これからも力を尽くします</t>
+          <t xml:space="preserve">あの存在がわたくしを高めてくれる。これが宿命というものかしら</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9148,14 +9148,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめております</t>
+          <t xml:space="preserve">戦えることに感謝を。けれど次は必ず勝ちます</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.ojousama[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9180,14 +9180,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じておりましたのに…もうここでは踏ん張れません</t>
+          <t xml:space="preserve">この団体に報いられるよう、これからも力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.ojousama[2]</t>
+          <t xml:space="preserve">trust_above_75.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くしてきたつもりです。けれど、もう…</t>
+          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめております</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9244,14 +9244,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の方針に…少し不安を覚えます</t>
+          <t xml:space="preserve">信じておりましたのに…もうここでは踏ん張れません</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.ojousama[2]</t>
+          <t xml:space="preserve">trust_below_20.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの居場所がここにあるのか…考えてしまいます</t>
+          <t xml:space="preserve">全力を尽くしてきたつもりです。けれど、もう…</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9308,14 +9308,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
+          <t xml:space="preserve">この団体の方針に…少し不安を覚えます</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9325,29 +9325,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.earnest[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
+          <t xml:space="preserve">わたくしの居場所がここにあるのか…考えてしまいます</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9357,29 +9357,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.earnest[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
+          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9404,14 +9404,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
+          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.earnest[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9436,14 +9436,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
+          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.earnest[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9468,14 +9468,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
+          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.earnest[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9500,14 +9500,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた?</t>
+          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">survivor.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9532,14 +9532,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
+          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.earnest[2]</t>
+          <t xml:space="preserve">survivor.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9564,14 +9564,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
+          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.earnest[1]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9596,14 +9596,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
+          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.earnest[2]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9628,14 +9628,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
+          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.earnest[1]</t>
+          <t xml:space="preserve">defiant.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
+          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.earnest[2]</t>
+          <t xml:space="preserve">defiant.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
+          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9724,14 +9724,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
+          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9756,14 +9756,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
+          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
@@ -9788,14 +9788,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てましたわ…！ みなさまのおかげですわ…！</t>
+          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のために全力を尽くせましたわ…嬉しいですわ</t>
+          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[3]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
+          <t xml:space="preserve">勝てました…！ みなさまのおかげですわ…！</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.earnest[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9869,29 +9869,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…感謝しかありませんの</t>
+          <t xml:space="preserve">団体のために全力を尽くせました…嬉しいですわ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9901,59 +9901,123 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">努力が報われましたわ…感謝しかありませんの</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr" s="2">
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr" s="12">
+      <c r="D304" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr" s="2">
+      <c r="E304" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr" s="3">
+      <c r="F304" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H302"/>
+  <autoFilter ref="A1:H304"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H304"/>
+  <dimension ref="A1:H311"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3904,7 +3904,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.ojousama.earnest[1]</t>
+          <t xml:space="preserve">decline_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝いたします。期待に応えてみせますわね。</t>
+          <t xml:space="preserve">承知いたしましたわ。見合う額をいただく——それが筋というものですから</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.ojousama.earnest[1]</t>
+          <t xml:space="preserve">decline_hold.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長のご判断を尊重いたします。精一杯やりますわね。</t>
+          <t xml:space="preserve">……それはいけませんわ。……いいえ、頂戴します。頂いた以上、もう逃げられません</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.ojousama.earnest[1]</t>
+          <t xml:space="preserve">decline_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……残念ですわ。ですが、この判断の結果はお忘れなきよう。</t>
+          <t xml:space="preserve">……はい。数字は数字ですもの。言い訳を並べるのは、かえって失礼でしょう</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.ojousama.earnest[1]</t>
+          <t xml:space="preserve">decline_strict.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}契約のことで筋を通させていただきたく存じますわ。{record}</t>
+          <t xml:space="preserve">……承知しました。……ですが、礼を欠いたのはどちらか、考えてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.ojousama.earnest[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしましたわ。ですが、このまま変わらなければ…。</t>
+          <t xml:space="preserve">ありがとうございます。……身の丈の額で戦えるのは、幸せなことですもの</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.ojousama.earnest[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お別れの時が参りました。どうか、お元気で。</t>
+          <t xml:space="preserve">……それでは道理が通りませんわ。……いいえ、頂きます。この借りは、リングで！</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.earnest[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.ojousama.earnest[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変お世話になりました。ですが、もう限界でございます。</t>
+          <t xml:space="preserve">社長。今の私に、以前と同じ額は不相応ですわ。どうか、正しく直してくださいまし</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.ojousama.earnest[1]</t>
+          <t xml:space="preserve">raise_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。{record}こちらでの経験は一生の宝ですわ。ですが…新天地で挑戦したいのです。</t>
+          <t xml:space="preserve">感謝いたします。期待に応えてみせますわね。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.ojousama.earnest[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4185,14 +4185,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}心苦しいのですが…退団を願い出たく存じますわ。</t>
+          <t xml:space="preserve">……社長のご判断を尊重いたします。精一杯やりますわね。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.ojousama.earnest[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4217,14 +4217,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしました。{tenure_farewell}こちらでの日々、忘れませんわ。{rivalry}</t>
+          <t xml:space="preserve">……残念ですわ。ですが、この判断の結果はお忘れなきよう。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.ojousama.earnest[1]</t>
+          <t xml:space="preserve">raise_open.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お気持ちは嬉しゅうございますわ。ですが…この決断は揺るぎません。申し訳ございません。</t>
+          <t xml:space="preserve">社長。{tenure}契約のことで筋を通させていただきたく存じますわ。{record}</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.ojousama.earnest[1]</t>
+          <t xml:space="preserve">raise_refuse.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4281,369 +4281,369 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……その誠意、しかと受け止めました。もう一度、全力で臨みますわ。</t>
+          <t xml:space="preserve">……承知いたしましたわ。ですが、このまま変わらなければ…。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お別れの時が参りました。どうか、お元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.ojousama.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">大変お世話になりました。ですが、もう限界でございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます。{record}こちらでの経験は一生の宝ですわ。ですが…新天地で挑戦したいのです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}心苦しいのですが…退団を願い出たく存じますわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知いたしました。{tenure_farewell}こちらでの日々、忘れませんわ。{rivalry}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お気持ちは嬉しゅうございますわ。ですが…この決断は揺るぎません。申し訳ございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……その誠意、しかと受け止めました。もう一度、全力で臨みますわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今の仲間への責任がありますわ。
 それを果たすまで、他のお話は聞けませんの</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="D134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="E134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">皆さまを置いて行くわけにはまいりませんわ</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr" s="12">
+      <c r="D135" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr" s="2">
+      <c r="E135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr" s="3">
+      <c r="F135" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">この団体を離れるのは容易ではありませんわ。
 …でも、お聞きするだけなら</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr" s="12">
+      <c r="D136" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr" s="2">
+      <c r="E136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr" s="3">
+      <c r="F136" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">新しい仲間のために…全力を尽くしますわ。
 よろしくお願いいたします</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、不躾ですが、わたくしどものメンバーをもう少しお気遣いいただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、不躾なお願いですが、次の興行のメインをわたくしたちにお任せいただきたく。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、お聞き苦しいかもしれませんが、わたくしどもの待遇を見直していただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、不躾なお願いですが、わたくしどもの貢献にひとことお言葉を頂戴したく。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、誠にありがとうございますわ。お言葉、大切にいたします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="40" customHeight="1">
-      <c r="A136" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
-        </is>
-      </c>
-    </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4668,14 +4668,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、誠にありがとうございます。粗相のないよう務めますわ。</t>
+          <t xml:space="preserve">社長、不躾ですが、わたくしどものメンバーをもう少しお気遣いいただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4700,14 +4700,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知いたしましたわ。失礼いたしました。</t>
+          <t xml:space="preserve">社長、不躾なお願いですが、次の興行のメインをわたくしたちにお任せいただきたく。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4732,14 +4732,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">社長、お聞き苦しいかもしれませんが、わたくしどもの待遇を見直していただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、誠にありがとうございます。皆を代表してお礼申し上げますわ。</t>
+          <t xml:space="preserve">社長、不躾なお願いですが、わたくしどもの貢献にひとことお言葉を頂戴したく。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
+          <t xml:space="preserve">社長、誠にありがとうございますわ。お言葉、大切にいたします。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4828,14 +4828,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、誠にありがとうございますわ。お言葉、大切にいたします。</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4892,14 +4892,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
+          <t xml:space="preserve">社長、誠にありがとうございます。粗相のないよう務めますわ。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…承知いたしましたわ。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4956,14 +4956,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。輪の外の子のお気持ち、見えてませんでしたわ。</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4988,14 +4988,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎぬよう気をつけますわ。</t>
+          <t xml:space="preserve">社長、誠にありがとうございます。皆を代表してお礼申し上げますわ。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません、心がけを改めますわ。</t>
+          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5052,14 +5052,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。リングの外にまで持ち込むのは、行きすぎでしたわ。</t>
+          <t xml:space="preserve">社長、誠にありがとうございますわ。お言葉、大切にいたします。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとういたしますわ。</t>
+          <t xml:space="preserve">…承知いたしましたわ。お聞き苦しいことを申しました。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5148,14 +5148,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。お恥ずかしい限りですの。</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5180,14 +5180,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。お見逃しのぶん、お返しいたしますわ。</t>
+          <t xml:space="preserve">…申し訳ありません。輪の外の子のお気持ち、見えてませんでしたわ。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5212,14 +5212,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎぬよう気をつけますわ。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5244,14 +5244,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。ご厚意に甘えさせていただきますわ。</t>
+          <t xml:space="preserve">…申し訳ありません、心がけを改めますわ。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5276,14 +5276,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。皆で支えていただけると、立ち直れますわ。</t>
+          <t xml:space="preserve">…申し訳ありません。リングの外にまで持ち込むのは、行きすぎでしたわ。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5340,14 +5340,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。わたくしの目が届きませんでしたわ。</t>
+          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとういたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5372,14 +5372,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。穏便に収まるよう努めますわ。</t>
+          <t xml:space="preserve">…申し訳ありませんわ。お恥ずかしい限りですの。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5404,14 +5404,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。お見逃しのぶん、お返しいたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5436,14 +5436,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありませんわ。心がけを改めます。</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5468,14 +5468,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…静かに会釈なさいましたわ）</t>
+          <t xml:space="preserve">…ありがとうございます。ご厚意に甘えさせていただきますわ。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5500,14 +5500,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てますわ。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5532,14 +5532,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。わたくしの判断が行きすぎましたわ。</t>
+          <t xml:space="preserve">…ありがとうございます。皆で支えていただけると、立ち直れますわ。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5564,14 +5564,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。責任はわたくしが持ちますわ。</t>
+          <t xml:space="preserve">…申し訳ありません。わたくしの目が届きませんでしたわ。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5596,14 +5596,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
+          <t xml:space="preserve">…ありがとうございます。穏便に収まるよう努めますわ。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.attack.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">けじめを、つけさせてくださいませ</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.defend.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5660,29 +5660,29 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるつもりはございませんわ</t>
+          <t xml:space="preserve">…申し訳ありませんわ。心がけを改めます。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5692,14 +5692,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来て、退く理由がございませんわ。</t>
+          <t xml:space="preserve">（…静かに会釈なさいましたわ）</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5709,29 +5709,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お稽古の成果です…！ まだまだ上を目指しますわ</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5741,29 +5741,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてまいりましたものが、形になりそうですわ</t>
+          <t xml:space="preserve">…申し訳ありません。わたくしの判断が行きすぎましたわ。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5773,29 +5773,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お稽古の成果が出てきましたわ</t>
+          <t xml:space="preserve">…ありがとうございます。責任はわたくしが持ちますわ。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5805,29 +5805,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日お稽古に通うのが…こんなに辛いとは</t>
+          <t xml:space="preserve">…社長、ご配慮痛み入りますわ。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.ojousama</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5837,29 +5837,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">earnest.attack.ojousama</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘う心を忘れていましたわ…でも、もう迷いませんの</t>
+          <t xml:space="preserve">けじめを、つけさせてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.ojousama</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5869,61 +5869,61 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">earnest.defend.ojousama</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしましたわ…必ずお返しいたします</t>
+          <t xml:space="preserve">逃げるつもりはございませんわ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの敗北…わたくしの何がいけませんでしたの</t>
+          <t xml:space="preserve">ここまで来て、退く理由がございませんわ。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.ojousama.earnest[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5948,14 +5948,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できましたのに…まだまだ足りませんわ</t>
+          <t xml:space="preserve">お稽古の成果です…！ まだまだ上を目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.ojousama.earnest[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5980,14 +5980,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できましたわ…でもお体が覚えていますの、あの痛みを</t>
+          <t xml:space="preserve">積み重ねてまいりましたものが、形になりそうですわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.ojousama.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ovr_growth.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6012,14 +6012,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お怪我は癒えましたわ。でも離れていた時間が…重いですの</t>
+          <t xml:space="preserve">お稽古の成果が出てきましたわ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6029,29 +6029,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体を代表する責任を果たせたことを、誇りに思いますわ。</t>
+          <t xml:space="preserve">毎日お稽古に通うのが…こんなに辛いとは</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6061,29 +6061,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合に向けて積み重ねた日々が報われましたわ。最高のお相手に感謝いたします</t>
+          <t xml:space="preserve">闘う心を忘れていましたわ…でも、もう迷いませんの</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6093,29 +6093,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どの試合にも全身全霊を注ぎますわ。それがわたくしの矜持です</t>
+          <t xml:space="preserve">ご迷惑をおかけしましたわ…必ずお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6125,29 +6125,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.ojousama.earnest[1]</t>
+          <t xml:space="preserve">defeat.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の皆さまへ。わたくしが歩んだ道を、どうか超えていってくださいまし</t>
+          <t xml:space="preserve">あの敗北…わたくしの何がいけませんでしたの</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6157,29 +6157,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.ojousama.earnest[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">弛まぬ努力の賜物ですわ。来年も精進を続けますの</t>
+          <t xml:space="preserve">復帰できましたのに…まだまだ足りませんわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6189,29 +6189,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.ojousama.earnest[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力を重ねてまいりました。この賞を糧に、さらなる高みを目指しますわ</t>
+          <t xml:space="preserve">復帰できましたわ…でもお体が覚えていますの、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6221,29 +6221,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">penalty_end.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒の献身に報いるためにも、この優勝を誇り高く受け取りますわ。</t>
+          <t xml:space="preserve">お怪我は癒えましたわ。でも離れていた時間が…重いですの</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">autumnWarChampion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6268,14 +6268,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングに立つ責任、重々承知しておりますわ</t>
+          <t xml:space="preserve">団体を代表する責任を果たせたことを、誇りに思いますわ。</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">bestMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6300,14 +6300,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じぬ試合を、必ずいたしますわ</t>
+          <t xml:space="preserve">あの試合に向けて積み重ねた日々が報われましたわ。最高のお相手に感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[3]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6332,14 +6332,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精進の成果、すべてお見せいたしますわ</t>
+          <t xml:space="preserve">どの試合にも全身全霊を注ぎますわ。それがわたくしの矜持です</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6364,14 +6364,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様、団体として誇らしい限りですわ</t>
+          <t xml:space="preserve">後輩の皆さまへ。わたくしが歩んだ道を、どうか超えていってくださいまし</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">mvp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この達成を糧に、さらに精進いたしますわ</t>
+          <t xml:space="preserve">弛まぬ努力の賜物ですわ。来年も精進を続けますの</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[3]</t>
+          <t xml:space="preserve">rookie.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6428,14 +6428,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気を緩めず、次に備えますの</t>
+          <t xml:space="preserve">努力を重ねてまいりました。この賞を糧に、さらなる高みを目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6445,29 +6445,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">springTagChampion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが大切です。一歩一歩、参りますわね</t>
+          <t xml:space="preserve">相棒の献身に報いるためにも、この優勝を誇り高く受け取りますわ。</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6477,29 +6477,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体でご一緒できる仲間がいて、幸せですわ</t>
+          <t xml:space="preserve">ドームのリングに立つ責任、重々承知しておりますわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6509,29 +6509,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお休みをいただければ、必ず立て直しますわ</t>
+          <t xml:space="preserve">団体の名に恥じぬ試合を、必ずいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6541,29 +6541,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆様のお声が力になりますわ</t>
+          <t xml:space="preserve">精進の成果、すべてお見せいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6573,29 +6573,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切りたいわけではありませんの。ただ……</t>
+          <t xml:space="preserve">満員のお客様、団体として誇らしい限りですわ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6605,29 +6605,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を重ねましても、何かが足りない気がしますの…</t>
+          <t xml:space="preserve">この達成を糧に、さらに精進いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6637,29 +6637,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…努力が足りないのかしら。でも…</t>
+          <t xml:space="preserve">気を緩めず、次に備えますの</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6669,29 +6669,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。結果でお応えしますわ</t>
+          <t xml:space="preserve">積み重ねが大切です。一歩一歩、参りますわね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6701,29 +6701,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みっちり鍛えていただきますわ！絶対に成長してみせますの</t>
+          <t xml:space="preserve">この団体でご一緒できる仲間がいて、幸せですわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6733,29 +6733,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくださったんですのね…お報いしますわ</t>
+          <t xml:space="preserve">少しお休みをいただければ、必ず立て直しますわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6765,29 +6765,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみますわ</t>
+          <t xml:space="preserve">ファンの皆様のお声が力になりますわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6797,29 +6797,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N5_low.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの不徳の致すところ、ということですわね</t>
+          <t xml:space="preserve">裏切りたいわけではありませんの。ただ……</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6829,29 +6829,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.ojousama.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の看板として恥ずかしくない姿をお見せしますわ</t>
+          <t xml:space="preserve">練習を重ねましても、何かが足りない気がしますの…</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6861,29 +6861,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.ojousama.earnest[1]</t>
+          <t xml:space="preserve">G1.voice.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、お疲れ様ですわ。明日からまた頑張りましょうね</t>
+          <t xml:space="preserve">…努力が足りないのかしら。でも…</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.ojousama.earnest[1]</t>
+          <t xml:space="preserve">bonus.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6908,14 +6908,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習のことが気になりますけれど…お心遣い、ありがとうございますわ</t>
+          <t xml:space="preserve">ありがとうございます。結果でお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.ojousama.earnest[1]</t>
+          <t xml:space="preserve">camp.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6940,14 +6940,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そこまでお気遣いを…必ずや復帰してお応えしますわ</t>
+          <t xml:space="preserve">みっちり鍛えていただきますわ！絶対に成長してみせますの</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.ojousama.earnest[1]</t>
+          <t xml:space="preserve">encourage_high_trust.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をいただけますなんて…全力でお応えしますわ</t>
+          <t xml:space="preserve">ずっと見てくださったんですのね…お報いしますわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">encourage.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7004,14 +7004,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビは緊張いたしますけれど…精一杯やらせていただきますわ</t>
+          <t xml:space="preserve">ありがとうございます…もう一度、頑張ってみますわ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.ojousama.earnest[1]</t>
+          <t xml:space="preserve">faction_decree.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらへの義理がございますから…でも、ご報告だけはと思いまして</t>
+          <t xml:space="preserve">わたくしの不徳の致すところ、ということですわね</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.earnest[1]</t>
+          <t xml:space="preserve">media.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7068,14 +7068,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…今日はどうしても、体が動かなくて…</t>
+          <t xml:space="preserve">団体の看板として恥ずかしくない姿をお見せしますわ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.earnest[2]</t>
+          <t xml:space="preserve">party.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">稽古に身が入らなくて…申し訳ありません…</t>
+          <t xml:space="preserve">皆様、お疲れ様ですわ。明日からまた頑張りましょうね</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.ojousama.earnest[1]</t>
+          <t xml:space="preserve">refresh_leave.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7132,14 +7132,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「わたくし、このままでよろしいのでしょうか」と後輩に弱音を漏らしている）</t>
+          <t xml:space="preserve">練習のことが気になりますけれど…お心遣い、ありがとうございますわ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.ojousama.earnest[1]</t>
+          <t xml:space="preserve">special_treatment.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7164,14 +7164,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「わたくしは本当に必要とされているのでしょうか」と率直な投稿）</t>
+          <t xml:space="preserve">そこまでお気遣いを…必ずや復帰してお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">trainer.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7196,14 +7196,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備してまいりましたの。チャンスをいただけませんこと</t>
+          <t xml:space="preserve">こんな機会をいただけますなんて…全力でお応えしますわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">E1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7228,14 +7228,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方を越えてこそですわ。組んでいただけませんこと</t>
+          <t xml:space="preserve">テレビは緊張いたしますけれど…精一杯やらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.ojousama.earnest[1]</t>
+          <t xml:space="preserve">E6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7260,14 +7260,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チームにご迷惑はかけたくありませんのに…体が限界ですわ…</t>
+          <t xml:space="preserve">こちらへの義理がございますから…でも、ご報告だけはと思いまして</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7292,14 +7292,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これまで耐えてまいりましたけれど…もう限界ですわ</t>
+          <t xml:space="preserve">申し訳ありません…今日はどうしても、体が動かなくて…</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7324,14 +7324,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何か申し上げようと口を開き、そっと閉じた）</t>
+          <t xml:space="preserve">稽古に身が入らなくて…申し訳ありません…</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S_grumble.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7356,14 +7356,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいですの。特訓のお許しをいただけませんこと</t>
+          <t xml:space="preserve">（「わたくし、このままでよろしいのでしょうか」と後輩に弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S_sns.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7388,14 +7388,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が学んできたことを、後輩にお伝えしたいと思いまして…</t>
+          <t xml:space="preserve">（SNSに「わたくしは本当に必要とされているのでしょうか」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7420,14 +7420,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと気をつけるべきでしたわ…早く復帰して見せますの</t>
+          <t xml:space="preserve">ずっと準備してまいりましたの。チャンスをいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7452,14 +7452,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…チームのためにもはっきりさせるべきですわ</t>
+          <t xml:space="preserve">あの方を越えてこそですわ。組んでいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S3.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7484,14 +7484,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体にご迷惑はかけたくありませんのに…あの方とは…</t>
+          <t xml:space="preserve">チームにご迷惑はかけたくありませんのに…体が限界ですわ…</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7516,14 +7516,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">品格を忘れず、ブランドのイメージを大切にしますわ</t>
+          <t xml:space="preserve">これまで耐えてまいりましたけれど…もう限界ですわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S4_silent.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7548,14 +7548,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり準備してお役目を果たしますわ</t>
+          <t xml:space="preserve">…………（何か申し上げようと口を開き、そっと閉じた）</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S5.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7580,14 +7580,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に誠実に向き合うことが私の務めですわ</t>
+          <t xml:space="preserve">もっと強くなりたいですの。特訓のお許しをいただけませんこと</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">S6.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイには自信がありますわ。しっかり務めます</t>
+          <t xml:space="preserve">私が学んできたことを、後輩にお伝えしたいと思いまして…</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7644,14 +7644,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">プロとして恥ずかしくない撮影ができるよう、準備します</t>
+          <t xml:space="preserve">もっと気をつけるべきでしたわ…早く復帰して見せますの</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter1.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7676,14 +7676,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言葉遣いには気をつけて、丁寧に対応しますわ</t>
+          <t xml:space="preserve">あの方とは…チームのためにもはっきりさせるべきですわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ojousama.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7708,14 +7708,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でよろしいのですか…？ 精一杯頑張りますわ</t>
+          <t xml:space="preserve">団体にご迷惑はかけたくありませんのに…あの方とは…</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7725,29 +7725,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_brand.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
+          <t xml:space="preserve">品格を忘れず、ブランドのイメージを大切にしますわ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7757,29 +7757,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_cm.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
+          <t xml:space="preserve">しっかり準備してお役目を果たしますわ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7789,29 +7789,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">B4_fan.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
+          <t xml:space="preserve">ファンの方々に誠実に向き合うことが私の務めですわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7821,29 +7821,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_fashion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
+          <t xml:space="preserve">ランウェイには自信がありますわ。しっかり務めます</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7853,29 +7853,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_gravure.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
+          <t xml:space="preserve">プロとして恥ずかしくない撮影ができるよう、準備します</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7885,29 +7885,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">B4_variety.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
+          <t xml:space="preserve">言葉遣いには気をつけて、丁寧に対応しますわ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7917,29 +7917,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">B4.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
+          <t xml:space="preserve">私でよろしいのですか…？ 精一杯頑張りますわ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7964,14 +7964,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">下ろしたはずの荷を、また持たされているみたいですわね</t>
+          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7996,14 +7996,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったことにされた分は、まだお返ししていませんの</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
+          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8060,14 +8060,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
+          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.earnest[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8092,14 +8092,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
+          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8124,14 +8124,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8156,14 +8156,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
+          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8188,14 +8188,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
+          <t xml:space="preserve">下ろしたはずの荷を、また持たされているみたいですわね</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8220,14 +8220,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
+          <t xml:space="preserve">終わったことにされた分は、まだお返ししていませんの</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.earnest[2]</t>
+          <t xml:space="preserve">draftInterest.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8252,14 +8252,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
+          <t xml:space="preserve">コツコツ積み重ねるのが信条ですの。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8284,14 +8284,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
+          <t xml:space="preserve">期待に応えられるよう、全力を尽くしますわ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.ojousama.earnest[1]</t>
+          <t xml:space="preserve">faGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8348,14 +8348,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
+          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.earnest[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
+          <t xml:space="preserve">ありがとうございますわ。ご期待に応えてみせますの</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.earnest[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8412,14 +8412,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
+          <t xml:space="preserve">コツコツ頑張りますわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.earnest[1]</t>
+          <t xml:space="preserve">injury.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
+          <t xml:space="preserve">ご期待に添えず、申し訳ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.earnest[1]</t>
+          <t xml:space="preserve">injury.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8476,14 +8476,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
+          <t xml:space="preserve">必ず、強くなって戻ってまいりますの</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">release.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8515,7 +8515,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8547,7 +8547,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8572,14 +8572,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
+          <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8604,14 +8604,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
+          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8636,14 +8636,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
+          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8668,14 +8668,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
+          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8685,29 +8685,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この関係…繕える自信がありません…</t>
+          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8717,29 +8717,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこで違えてしまったのでしょう…</t>
+          <t xml:space="preserve">応援くださった皆様に、申し訳ありませんわ…必ず次で</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8749,29 +8749,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この距離…わたくしの何がいけなかったのでしょう</t>
+          <t xml:space="preserve">短い間ですが、精一杯お務めいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8781,29 +8781,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度分かり合えるよう、努めなければ</t>
+          <t xml:space="preserve">実力が足りませんでしたわ…もっと精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8813,29 +8813,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切磋琢磨できること、光栄ですわ</t>
+          <t xml:space="preserve">防衛できましたわ。でもまだ満足はしませんの</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8845,29 +8845,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">共に頂を目指したい。二人ならきっと届きます</t>
+          <t xml:space="preserve">実力が足りませんでしたわ。一から出直しますの</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8877,29 +8877,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またとない相方。この巡り合わせに感謝を</t>
+          <t xml:space="preserve">努力が報われましたわ…！このベルト、大切にしますの</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8924,14 +8924,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関わりも変わりました。前へ進みましょう</t>
+          <t xml:space="preserve">この関係…繕える自信がありません…</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[2]</t>
+          <t xml:space="preserve">bond_39_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8956,14 +8956,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁から学んだことは多い。次の目標を探さねば</t>
+          <t xml:space="preserve">どこで違えてしまったのでしょう…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8988,14 +8988,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好敵手として意識している自分がおります</t>
+          <t xml:space="preserve">この距離…わたくしの何がいけなかったのでしょう</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">bond_59_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9020,14 +9020,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方を超えることが、今の一番の目標です</t>
+          <t xml:space="preserve">もう一度分かり合えるよう、努めなければ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_60_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この壁を越えぬ限り、わたくしに先はありません</t>
+          <t xml:space="preserve">切磋琢磨できること、光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">bond_80_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9084,14 +9084,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最大の壁。だからこそ、越えねばならないのです</t>
+          <t xml:space="preserve">共に頂を目指したい。二人ならきっと届きます</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9116,14 +9116,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの存在がわたくしを高めてくれる。これが宿命というものかしら</t>
+          <t xml:space="preserve">またとない相方。この巡り合わせに感謝を</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9148,14 +9148,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戦えることに感謝を。けれど次は必ず勝ちます</t>
+          <t xml:space="preserve">関わりも変わりました。前へ進みましょう</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9180,14 +9180,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に報いられるよう、これからも力を尽くします</t>
+          <t xml:space="preserve">あの因縁から学んだことは多い。次の目標を探さねば</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめております</t>
+          <t xml:space="preserve">好敵手として意識している自分がおります</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9244,14 +9244,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じておりましたのに…もうここでは踏ん張れません</t>
+          <t xml:space="preserve">あの方を超えることが、今の一番の目標です</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くしてきたつもりです。けれど、もう…</t>
+          <t xml:space="preserve">この壁を越えぬ限り、わたくしに先はありません</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9308,14 +9308,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の方針に…少し不安を覚えます</t>
+          <t xml:space="preserve">最大の壁。だからこそ、越えねばならないのです</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9340,14 +9340,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの居場所がここにあるのか…考えてしまいます</t>
+          <t xml:space="preserve">あの存在がわたくしを高めてくれる。これが宿命というものかしら</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9372,14 +9372,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
+          <t xml:space="preserve">戦えることに感謝を。けれど次は必ず勝ちます</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9389,29 +9389,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.earnest[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
+          <t xml:space="preserve">この団体に報いられるよう、これからも力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9421,29 +9421,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.earnest[2]</t>
+          <t xml:space="preserve">trust_above_75.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
+          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめております</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9453,29 +9453,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
+          <t xml:space="preserve">信じておりましたのに…もうここでは踏ん張れません</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9485,29 +9485,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.earnest[2]</t>
+          <t xml:space="preserve">trust_below_20.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
+          <t xml:space="preserve">全力を尽くしてきたつもりです。けれど、もう…</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9517,29 +9517,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.earnest[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.ojousama[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
+          <t xml:space="preserve">この団体の方針に…少し不安を覚えます</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9549,29 +9549,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.earnest[2]</t>
+          <t xml:space="preserve">trust_below_35.earnest.ojousama[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた？</t>
+          <t xml:space="preserve">わたくしの居場所がここにあるのか…考えてしまいます</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9581,29 +9581,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
+          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.earnest[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9628,14 +9628,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
+          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.earnest[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
+          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.earnest[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
+          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.earnest[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9724,14 +9724,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
+          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.earnest[2]</t>
+          <t xml:space="preserve">survivor.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9756,14 +9756,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
+          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">survivor.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9788,14 +9788,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
+          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
+          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9837,12 +9837,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました…！ みなさまのおかげですわ…！</t>
+          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">defiant.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9884,14 +9884,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のために全力を尽くせました…嬉しいですわ</t>
+          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[3]</t>
+          <t xml:space="preserve">defiant.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
+          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9933,29 +9933,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…感謝しかありませんの</t>
+          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9965,59 +9965,283 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てました…！ みなさまのおかげですわ…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体のために全力を尽くせました…嬉しいですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[3]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">努力が報われましたわ…感謝しかありませんの</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr" s="2">
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr" s="12">
+      <c r="D311" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr" s="2">
+      <c r="E311" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr" s="3">
+      <c r="F311" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H304"/>
+  <autoFilter ref="A1:H311"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H304"/>
+  <dimension ref="A1:H308"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9347,7 +9347,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9372,14 +9372,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
+          <t xml:space="preserve">……素晴らしい試合でしたわ、ありがとうございましたの</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9389,29 +9389,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
+          <t xml:space="preserve">……皆様のおかげですわ。本当に、本当に、ありがとうございますの</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9421,29 +9421,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.earnest[2]</t>
+          <t xml:space="preserve">GL-01.loss.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
+          <t xml:space="preserve">……申し訳、ございませんわ……</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9453,29 +9453,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.earnest[1]</t>
+          <t xml:space="preserve">GL-01.win.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
+          <t xml:space="preserve">ありがとうございますわ……皆様の声援、確かに届きましたの</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9485,29 +9485,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.earnest[2]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
+          <t xml:space="preserve">絶好調の時期を糧に、さらなる高みを目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.earnest[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9532,14 +9532,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
+          <t xml:space="preserve">お仲間が繋いでくださった分、最後はわたくしが。傷など、後で数えますわ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.earnest[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9564,14 +9564,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた？</t>
+          <t xml:space="preserve">ここまで参りましたのだから。最後の一戦、全力でお応えいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9581,12 +9581,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9596,14 +9596,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
+          <t xml:space="preserve">どなたがお相手でも、全力で臨みますわ。それが礼儀ですもの</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.earnest[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9628,14 +9628,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
+          <t xml:space="preserve">この一戦に、気を緩めるところなど一つもありませんの</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.earnest[1]</t>
+          <t xml:space="preserve">survivor.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
+          <t xml:space="preserve">一人、お相手しましたわ。…息は乱れていますけれど、まだ役目の途中。次の方、いらして</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.earnest[2]</t>
+          <t xml:space="preserve">survivor.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
+          <t xml:space="preserve">まだ立っていますのよ。繋ぐまで、退くわけには参りませんの。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.earnest[1]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9724,14 +9724,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
+          <t xml:space="preserve">お二人から託された想いを、わたくしが最後まで守り通しましたわ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.earnest[2]</t>
+          <t xml:space="preserve">champion.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9756,14 +9756,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
+          <t xml:space="preserve">三人で約束した勝利ですの。わたくし一人の手柄にはいたしません</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">defiant.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9788,14 +9788,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
+          <t xml:space="preserve">お評価いただけるのは光栄ですわ。ですが、次は団体の勝利をお見せしますの</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">defiant.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
+          <t xml:space="preserve">仲間を勝たせられなかった悔しさ……この借りは、必ず返しますわ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9837,12 +9837,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました…！ みなさまのおかげですわ…！</t>
+          <t xml:space="preserve">お一人お一人に全力でお応えしましたわ。それがわたくしの礼儀ですもの</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.earnest[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9884,14 +9884,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のために全力を尽くせました…嬉しいですわ</t>
+          <t xml:space="preserve">限界は何度も感じましたわ。ですが……ここで退くのは、筋が通りませんの</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[3]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.earnest[3]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
+          <t xml:space="preserve">全力で参りますわ。よろしくお願いいたしますの</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.earnest[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9933,29 +9933,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.earnest[1]</t>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が報われましたわ…感謝しかありませんの</t>
+          <t xml:space="preserve">ここまで来られましたのは、皆様のおかげですわ。本当に、ありがとうございますの</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.earnest[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
@@ -9975,49 +9975,177 @@
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+          <t xml:space="preserve">勝てました…！ みなさまのおかげですわ…！</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体のために全力を尽くせました…嬉しいですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.earnest[3]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[3]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みなさまのおかげで勝てましたわ…感謝いたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">努力が報われましたわ…感謝しかありませんの</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">頂いた機会、決して粗末にいたしません</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr" s="2">
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr" s="12">
+      <c r="D308" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.earnest[1]</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr" s="2">
+      <c r="E308" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr" s="3">
+      <c r="F308" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">見込んでいただいた期待、一つずつ形にしてまいります</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H304"/>
+  <autoFilter ref="A1:H308"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×真面目.xlsx
@@ -2361,7 +2361,7 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お願いがあります。あの方と戦わせてください。</t>
+          <t xml:space="preserve">社長、お願いがあります。三人であちらへ挑ませてください。</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくし、あの方と対戦したいのです。どうか。</t>
+          <t xml:space="preserve">わたくしたち三人で、あちらへ挑みたいのです。どうか。</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">願いはひとつです。あの方と、当たらせてください。</t>
+          <t xml:space="preserve">願いはひとつです。三人で、あちらへ向かわせてください。</t>
         </is>
       </c>
     </row>
